--- a/public/exports/29189854.xlsx
+++ b/public/exports/29189854.xlsx
@@ -181,16 +181,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">312318</t>
+          <t xml:space="preserve">309127, 309128, 309129</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F4">
-        <v>1602</v>
+        <v>5924</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -231,7 +231,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777400</t>
+          <t xml:space="preserve">310466, 310467</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -240,7 +240,7 @@
         </is>
       </c>
       <c r="F5">
-        <v>3413</v>
+        <v>1428</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -281,16 +281,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">737430, 1808354</t>
+          <t xml:space="preserve">311019</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F6">
-        <v>442</v>
+        <v>815</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -331,16 +331,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">7374968</t>
+          <t xml:space="preserve">312318</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F7">
-        <v>275</v>
+        <v>1602</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -381,16 +381,16 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">737512, 5250365</t>
+          <t xml:space="preserve">312951, 312952</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F8">
-        <v>492</v>
+        <v>1169</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -431,16 +431,16 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">737561, 5238011</t>
+          <t xml:space="preserve">5777400</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F9">
-        <v>252</v>
+        <v>3413</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -481,16 +481,16 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">737569, 5248732</t>
+          <t xml:space="preserve">7374968</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F10">
-        <v>1777</v>
+        <v>275</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -531,7 +531,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">737574, 5248449</t>
+          <t xml:space="preserve">737561, 5238011</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="F11">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -581,16 +581,16 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">737864, 8331725</t>
+          <t xml:space="preserve">737569, 5248732</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F12">
-        <v>312</v>
+        <v>1777</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -631,16 +631,16 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">9120213</t>
+          <t xml:space="preserve">737574, 5248449</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F13">
-        <v>1054</v>
+        <v>279</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -681,16 +681,16 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">9345287</t>
+          <t xml:space="preserve">737864, 8331725</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F14">
-        <v>255</v>
+        <v>312</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -731,30 +731,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">8158787</t>
+          <t xml:space="preserve">9120213</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F15">
-        <v>413</v>
+        <v>1054</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">200008435</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018-10-29</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -781,30 +781,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">5779584</t>
+          <t xml:space="preserve">9345287</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F16">
-        <v>1234</v>
+        <v>255</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">200010724</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-02-18</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777338</t>
+          <t xml:space="preserve">8158787</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -840,16 +840,16 @@
         </is>
       </c>
       <c r="F17">
-        <v>822</v>
+        <v>413</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">200028497</t>
+          <t xml:space="preserve">200008435</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-24</t>
+          <t xml:space="preserve">2018-10-29</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">310466, 310467</t>
+          <t xml:space="preserve">5779584</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -890,16 +890,16 @@
         </is>
       </c>
       <c r="F18">
-        <v>1428</v>
+        <v>1234</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">310012200</t>
+          <t xml:space="preserve">200014490</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-11-06</t>
+          <t xml:space="preserve">2019-06-03</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">100049386</t>
+          <t xml:space="preserve">5777338</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -940,16 +940,16 @@
         </is>
       </c>
       <c r="F19">
-        <v>547</v>
+        <v>822</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">311098080</t>
+          <t xml:space="preserve">200028497</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-03-02</t>
+          <t xml:space="preserve">2020-02-24</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -981,35 +981,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">5263733</t>
+          <t xml:space="preserve">737512, 5250365</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F20">
-        <v>534</v>
+        <v>492</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">311358212</t>
+          <t xml:space="preserve">200030398</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-06</t>
+          <t xml:space="preserve">2020-04-16</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777441</t>
+          <t xml:space="preserve">100049386</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1040,26 +1040,26 @@
         </is>
       </c>
       <c r="F21">
-        <v>13747</v>
+        <v>547</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">311384248</t>
+          <t xml:space="preserve">311098080</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-06-24</t>
+          <t xml:space="preserve">2025-03-02</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -1081,25 +1081,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">10006074</t>
+          <t xml:space="preserve">5263733</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F22">
-        <v>381</v>
+        <v>534</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">311385901</t>
+          <t xml:space="preserve">311358212</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-02</t>
+          <t xml:space="preserve">2029-02-06</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">5256718</t>
+          <t xml:space="preserve">5777441</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1140,16 +1140,16 @@
         </is>
       </c>
       <c r="F23">
-        <v>7580</v>
+        <v>13747</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311434534</t>
+          <t xml:space="preserve">311384248</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-04-27</t>
+          <t xml:space="preserve">2029-06-24</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1181,25 +1181,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">5250298</t>
+          <t xml:space="preserve">10006074</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F24">
-        <v>626</v>
+        <v>381</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311498610</t>
+          <t xml:space="preserve">311385901</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-25</t>
+          <t xml:space="preserve">2029-07-02</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1231,25 +1231,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5242501</t>
+          <t xml:space="preserve">5256718</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F25">
-        <v>1439</v>
+        <v>7580</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311522367</t>
+          <t xml:space="preserve">311436528</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-25</t>
+          <t xml:space="preserve">2030-05-06</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1281,25 +1281,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5242501</t>
+          <t xml:space="preserve">5250298</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F26">
-        <v>3702</v>
+        <v>626</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311522367</t>
+          <t xml:space="preserve">311498610</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-25</t>
+          <t xml:space="preserve">2031-02-25</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1331,20 +1331,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">5242501</t>
+          <t xml:space="preserve">5777076</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F27">
-        <v>1390</v>
+        <v>452</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311522367</t>
+          <t xml:space="preserve">311522368</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777076</t>
+          <t xml:space="preserve">9643472</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1390,11 +1390,11 @@
         </is>
       </c>
       <c r="F28">
-        <v>452</v>
+        <v>2743</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311522368</t>
+          <t xml:space="preserve">311522375</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1436,15 +1436,15 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F29">
-        <v>2743</v>
+        <v>1267</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311522375</t>
+          <t xml:space="preserve">311522371</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1486,20 +1486,20 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F30">
-        <v>1267</v>
+        <v>847</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311522371</t>
+          <t xml:space="preserve">311578480</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-25</t>
+          <t xml:space="preserve">2032-02-13</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F31">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311578480</t>
+          <t xml:space="preserve">311578481</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1586,20 +1586,20 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F32">
-        <v>847</v>
+        <v>602</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311578481</t>
+          <t xml:space="preserve">311578773</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-13</t>
+          <t xml:space="preserve">2032-02-15</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1631,25 +1631,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">9643472</t>
+          <t xml:space="preserve">8073695</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F33">
-        <v>602</v>
+        <v>555</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311578773</t>
+          <t xml:space="preserve">311601866</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-15</t>
+          <t xml:space="preserve">2032-05-20</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1681,25 +1681,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">8073695</t>
+          <t xml:space="preserve">5262648</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F34">
-        <v>555</v>
+        <v>2330</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601866</t>
+          <t xml:space="preserve">311644250</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-20</t>
+          <t xml:space="preserve">2032-11-22</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">5262648</t>
+          <t xml:space="preserve">5248731</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1740,16 +1740,16 @@
         </is>
       </c>
       <c r="F35">
-        <v>2330</v>
+        <v>316</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644250</t>
+          <t xml:space="preserve">311650397</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-22</t>
+          <t xml:space="preserve">2032-12-20</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">312951, 312952</t>
+          <t xml:space="preserve">5262575</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1790,11 +1790,11 @@
         </is>
       </c>
       <c r="F36">
-        <v>1169</v>
+        <v>336</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650395</t>
+          <t xml:space="preserve">311650394</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">5248731</t>
+          <t xml:space="preserve">100044523</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1840,16 +1840,16 @@
         </is>
       </c>
       <c r="F37">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650397</t>
+          <t xml:space="preserve">311653972</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-20</t>
+          <t xml:space="preserve">2033-01-13</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1881,25 +1881,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">5262575</t>
+          <t xml:space="preserve">5256718</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="F38">
-        <v>336</v>
+        <v>778</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650394</t>
+          <t xml:space="preserve">311654332</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-20</t>
+          <t xml:space="preserve">2033-01-16</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -1931,25 +1931,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">100044523</t>
+          <t xml:space="preserve">5256718</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F39">
-        <v>334</v>
+        <v>665</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311653972</t>
+          <t xml:space="preserve">311654333</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-13</t>
+          <t xml:space="preserve">2033-01-16</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -1981,25 +1981,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">5256718</t>
+          <t xml:space="preserve">5262778</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F40">
-        <v>778</v>
+        <v>558</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654332</t>
+          <t xml:space="preserve">311654619</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-16</t>
+          <t xml:space="preserve">2033-01-18</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2031,25 +2031,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">5256718</t>
+          <t xml:space="preserve">5242741</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F41">
-        <v>665</v>
+        <v>338</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654333</t>
+          <t xml:space="preserve">311661169</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-16</t>
+          <t xml:space="preserve">2033-02-20</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2081,25 +2081,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">5262778</t>
+          <t xml:space="preserve">5243879</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F42">
-        <v>558</v>
+        <v>814</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654619</t>
+          <t xml:space="preserve">311661163</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-18</t>
+          <t xml:space="preserve">2033-02-20</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2131,20 +2131,20 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">5242741</t>
+          <t xml:space="preserve">5248692</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F43">
-        <v>338</v>
+        <v>3970</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661169</t>
+          <t xml:space="preserve">311661158</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">5243879</t>
+          <t xml:space="preserve">5263423</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2190,11 +2190,11 @@
         </is>
       </c>
       <c r="F44">
-        <v>814</v>
+        <v>348</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661163</t>
+          <t xml:space="preserve">311661161</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2231,25 +2231,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">5248692</t>
+          <t xml:space="preserve">5235664</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F45">
-        <v>3970</v>
+        <v>319</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661158</t>
+          <t xml:space="preserve">311661637</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-20</t>
+          <t xml:space="preserve">2033-02-22</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">5263423</t>
+          <t xml:space="preserve">5242835</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2290,16 +2290,16 @@
         </is>
       </c>
       <c r="F46">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661161</t>
+          <t xml:space="preserve">311661649</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-20</t>
+          <t xml:space="preserve">2033-02-22</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">5235664</t>
+          <t xml:space="preserve">5270230</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2340,11 +2340,11 @@
         </is>
       </c>
       <c r="F47">
-        <v>319</v>
+        <v>1798</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661637</t>
+          <t xml:space="preserve">311661646</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2381,20 +2381,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">5242501</t>
+          <t xml:space="preserve">5270230</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F48">
-        <v>1466</v>
+        <v>516</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661648</t>
+          <t xml:space="preserve">311661646</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2431,20 +2431,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">5242835</t>
+          <t xml:space="preserve">5270230</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F49">
-        <v>357</v>
+        <v>409</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661649</t>
+          <t xml:space="preserve">311661642</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">5270230</t>
+          <t xml:space="preserve">9073631</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2490,11 +2490,11 @@
         </is>
       </c>
       <c r="F50">
-        <v>1798</v>
+        <v>3104</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661646</t>
+          <t xml:space="preserve">311661636</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2531,25 +2531,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">5270230</t>
+          <t xml:space="preserve">9734086</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F51">
-        <v>516</v>
+        <v>829</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661646</t>
+          <t xml:space="preserve">311661950</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-22</t>
+          <t xml:space="preserve">2033-02-23</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2581,25 +2581,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">5270230</t>
+          <t xml:space="preserve">9734086</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F52">
-        <v>409</v>
+        <v>364</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661642</t>
+          <t xml:space="preserve">311661950</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-22</t>
+          <t xml:space="preserve">2033-02-23</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">9073631</t>
+          <t xml:space="preserve">5235995</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2640,16 +2640,16 @@
         </is>
       </c>
       <c r="F53">
-        <v>3104</v>
+        <v>4022</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661636</t>
+          <t xml:space="preserve">311667969</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-22</t>
+          <t xml:space="preserve">2033-03-21</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">9734086</t>
+          <t xml:space="preserve">5243876</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2690,16 +2690,16 @@
         </is>
       </c>
       <c r="F54">
-        <v>829</v>
+        <v>1027</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661950</t>
+          <t xml:space="preserve">311668049</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-23</t>
+          <t xml:space="preserve">2033-03-21</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2731,25 +2731,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">9734086</t>
+          <t xml:space="preserve">9319699</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F55">
-        <v>364</v>
+        <v>1216</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661950</t>
+          <t xml:space="preserve">311667988</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-23</t>
+          <t xml:space="preserve">2033-03-21</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2781,20 +2781,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">5235995</t>
+          <t xml:space="preserve">9319699</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F56">
-        <v>4022</v>
+        <v>524</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311667969</t>
+          <t xml:space="preserve">311667989</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">5243876</t>
+          <t xml:space="preserve">8073695</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2840,16 +2840,16 @@
         </is>
       </c>
       <c r="F57">
-        <v>1027</v>
+        <v>406</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311668049</t>
+          <t xml:space="preserve">311668436</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-21</t>
+          <t xml:space="preserve">2033-03-22</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2881,25 +2881,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">9319699</t>
+          <t xml:space="preserve">8073695</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F58">
-        <v>1216</v>
+        <v>935</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311667988</t>
+          <t xml:space="preserve">311668438</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-21</t>
+          <t xml:space="preserve">2033-03-22</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2931,25 +2931,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">9319699</t>
+          <t xml:space="preserve">5242501</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F59">
-        <v>524</v>
+        <v>1466</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311667989</t>
+          <t xml:space="preserve">311670158</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-21</t>
+          <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2981,25 +2981,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">8073695</t>
+          <t xml:space="preserve">5242501</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F60">
-        <v>406</v>
+        <v>1439</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311668436</t>
+          <t xml:space="preserve">311670158</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-22</t>
+          <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">8073695</t>
+          <t xml:space="preserve">5242501</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3040,16 +3040,16 @@
         </is>
       </c>
       <c r="F61">
-        <v>935</v>
+        <v>3702</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311668438</t>
+          <t xml:space="preserve">311670158</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-22</t>
+          <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3081,20 +3081,20 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">5270632</t>
+          <t xml:space="preserve">5242501</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F62">
-        <v>608</v>
+        <v>1390</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670156</t>
+          <t xml:space="preserve">311670158</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">5274226</t>
+          <t xml:space="preserve">5270632</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3140,11 +3140,11 @@
         </is>
       </c>
       <c r="F63">
-        <v>854</v>
+        <v>608</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670155</t>
+          <t xml:space="preserve">311670156</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5274894</t>
+          <t xml:space="preserve">5274226</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3190,11 +3190,11 @@
         </is>
       </c>
       <c r="F64">
-        <v>2071</v>
+        <v>854</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670153</t>
+          <t xml:space="preserve">311670155</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3231,20 +3231,20 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">8162582</t>
+          <t xml:space="preserve">5274894</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F65">
-        <v>1072</v>
+        <v>2071</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670165</t>
+          <t xml:space="preserve">311670153</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3286,15 +3286,15 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F66">
-        <v>408</v>
+        <v>1072</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670164</t>
+          <t xml:space="preserve">311670161</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F67">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670164</t>
+          <t xml:space="preserve">311670161</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F68">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670164</t>
+          <t xml:space="preserve">311670161</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F69">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670164</t>
+          <t xml:space="preserve">311670161</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3481,20 +3481,20 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">9345395</t>
+          <t xml:space="preserve">8162582</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="F70">
-        <v>2157</v>
+        <v>408</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670236</t>
+          <t xml:space="preserve">311670161</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3536,15 +3536,15 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F71">
-        <v>267</v>
+        <v>2157</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670238</t>
+          <t xml:space="preserve">311670236</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3581,25 +3581,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">5248471</t>
+          <t xml:space="preserve">9345395</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F72">
-        <v>358</v>
+        <v>267</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670600</t>
+          <t xml:space="preserve">311670238</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-30</t>
+          <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3636,15 +3636,15 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F73">
-        <v>862</v>
+        <v>358</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670599</t>
+          <t xml:space="preserve">311670600</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3681,20 +3681,20 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040385</t>
+          <t xml:space="preserve">5248471</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F74">
-        <v>470</v>
+        <v>862</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670603</t>
+          <t xml:space="preserve">311670599</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3731,25 +3731,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">9120321</t>
+          <t xml:space="preserve">8040385</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F75">
-        <v>2095</v>
+        <v>470</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311673018</t>
+          <t xml:space="preserve">311670603</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-12</t>
+          <t xml:space="preserve">2033-03-30</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3786,11 +3786,11 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F76">
-        <v>806</v>
+        <v>2095</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3836,11 +3836,11 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F77">
-        <v>2646</v>
+        <v>806</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3881,25 +3881,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">5260034</t>
+          <t xml:space="preserve">9120321</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F78">
-        <v>1438</v>
+        <v>2646</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311679002</t>
+          <t xml:space="preserve">311673018</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-08</t>
+          <t xml:space="preserve">2033-04-12</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3931,20 +3931,20 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">9069219</t>
+          <t xml:space="preserve">5260034</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F79">
-        <v>314</v>
+        <v>1438</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311678991</t>
+          <t xml:space="preserve">311679002</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3986,11 +3986,11 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F80">
-        <v>510</v>
+        <v>314</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -4036,11 +4036,11 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F81">
-        <v>268</v>
+        <v>510</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -4081,25 +4081,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">5260044</t>
+          <t xml:space="preserve">9069219</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F82">
-        <v>1419</v>
+        <v>268</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311679338</t>
+          <t xml:space="preserve">311678991</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-09</t>
+          <t xml:space="preserve">2033-05-08</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311019</t>
+          <t xml:space="preserve">5254271</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4540,16 +4540,16 @@
         </is>
       </c>
       <c r="F91">
-        <v>815</v>
+        <v>415</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311717620</t>
+          <t xml:space="preserve">311763725</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-25</t>
+          <t xml:space="preserve">2034-06-03</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4586,15 +4586,15 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F92">
-        <v>415</v>
+        <v>1536</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763725</t>
+          <t xml:space="preserve">311763724</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4636,15 +4636,15 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F93">
-        <v>1536</v>
+        <v>452</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763724</t>
+          <t xml:space="preserve">311763725</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4681,20 +4681,20 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">5254271</t>
+          <t xml:space="preserve">5254347</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F94">
-        <v>452</v>
+        <v>520</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763725</t>
+          <t xml:space="preserve">311763739</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4731,20 +4731,20 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">5254347</t>
+          <t xml:space="preserve">5255563</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F95">
-        <v>520</v>
+        <v>868</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763739</t>
+          <t xml:space="preserve">311763694</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">5255563</t>
+          <t xml:space="preserve">5255617</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4790,11 +4790,11 @@
         </is>
       </c>
       <c r="F96">
-        <v>868</v>
+        <v>278</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763694</t>
+          <t xml:space="preserve">311763693</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">5255617</t>
+          <t xml:space="preserve">5268254</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -4840,11 +4840,11 @@
         </is>
       </c>
       <c r="F97">
-        <v>278</v>
+        <v>1015</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763693</t>
+          <t xml:space="preserve">311763726</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4881,20 +4881,20 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">5268254</t>
+          <t xml:space="preserve">5268269</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F98">
-        <v>1015</v>
+        <v>262</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763726</t>
+          <t xml:space="preserve">311763735</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4936,11 +4936,11 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F99">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -4981,20 +4981,20 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">5268269</t>
+          <t xml:space="preserve">5775323</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F100">
-        <v>258</v>
+        <v>2574</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763735</t>
+          <t xml:space="preserve">311763728</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -5031,20 +5031,20 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">5775323</t>
+          <t xml:space="preserve">5775595</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F101">
-        <v>2574</v>
+        <v>2589</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763728</t>
+          <t xml:space="preserve">311763897</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -5086,15 +5086,15 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F102">
-        <v>2589</v>
+        <v>3338</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763897</t>
+          <t xml:space="preserve">311763900</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -5131,20 +5131,20 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">5775595</t>
+          <t xml:space="preserve">7747263</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F103">
-        <v>3338</v>
+        <v>2087</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763900</t>
+          <t xml:space="preserve">311763695</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">7747263</t>
+          <t xml:space="preserve">9303236</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -5190,11 +5190,11 @@
         </is>
       </c>
       <c r="F104">
-        <v>2087</v>
+        <v>677</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763695</t>
+          <t xml:space="preserve">311763696</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">9303236</t>
+          <t xml:space="preserve">5247379</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="F105">
-        <v>677</v>
+        <v>564</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763696</t>
+          <t xml:space="preserve">311764473</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-06-03</t>
+          <t xml:space="preserve">2034-06-06</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5286,15 +5286,15 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F106">
-        <v>564</v>
+        <v>1639</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311764474</t>
+          <t xml:space="preserve">311764473</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -5331,20 +5331,20 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">5247379</t>
+          <t xml:space="preserve">5250365</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F107">
-        <v>1639</v>
+        <v>4382</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311764474</t>
+          <t xml:space="preserve">311764478</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -5386,11 +5386,11 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F108">
-        <v>4382</v>
+        <v>1154</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -5436,15 +5436,15 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F109">
-        <v>1154</v>
+        <v>1483</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311764478</t>
+          <t xml:space="preserve">311764476</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -5481,20 +5481,20 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">5250365</t>
+          <t xml:space="preserve">8662006</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F110">
-        <v>1483</v>
+        <v>1769</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311764476</t>
+          <t xml:space="preserve">311764471</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5536,11 +5536,11 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F111">
-        <v>1769</v>
+        <v>1063</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -5586,11 +5586,11 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F112">
-        <v>1063</v>
+        <v>275</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -5631,25 +5631,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">8662006</t>
+          <t xml:space="preserve">5254347</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F113">
-        <v>275</v>
+        <v>326</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311764471</t>
+          <t xml:space="preserve">311764844</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-06-06</t>
+          <t xml:space="preserve">2034-06-07</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5686,11 +5686,11 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F114">
-        <v>326</v>
+        <v>1272</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -5731,25 +5731,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">5254347</t>
+          <t xml:space="preserve">5254851</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F115">
-        <v>1272</v>
+        <v>1054</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311764844</t>
+          <t xml:space="preserve">311766708</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-06-07</t>
+          <t xml:space="preserve">2034-06-14</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -5786,15 +5786,15 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F116">
-        <v>1054</v>
+        <v>1406</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766708</t>
+          <t xml:space="preserve">311766710</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5831,20 +5831,20 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">5254851</t>
+          <t xml:space="preserve">5255997</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F117">
-        <v>1406</v>
+        <v>293</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766710</t>
+          <t xml:space="preserve">311766615</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -5881,20 +5881,20 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">5255997</t>
+          <t xml:space="preserve">5256718</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F118">
-        <v>293</v>
+        <v>1396</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766615</t>
+          <t xml:space="preserve">311766630</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -5936,11 +5936,11 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
       <c r="F119">
-        <v>1396</v>
+        <v>1087</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -5986,11 +5986,11 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F120">
-        <v>1087</v>
+        <v>619</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -6031,20 +6031,20 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">5256718</t>
+          <t xml:space="preserve">5260532</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F121">
-        <v>619</v>
+        <v>4077</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766630</t>
+          <t xml:space="preserve">311766620</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -6081,20 +6081,20 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">5260532</t>
+          <t xml:space="preserve">5777400</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F122">
-        <v>4077</v>
+        <v>2585</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766620</t>
+          <t xml:space="preserve">311766632</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -6136,11 +6136,11 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F123">
-        <v>2585</v>
+        <v>1285</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -6186,11 +6186,11 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F124">
-        <v>1285</v>
+        <v>5606</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -6231,20 +6231,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777400</t>
+          <t xml:space="preserve">5777914</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F125">
-        <v>5606</v>
+        <v>406</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766632</t>
+          <t xml:space="preserve">311766606</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777914</t>
+          <t xml:space="preserve">5780012</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -6290,11 +6290,11 @@
         </is>
       </c>
       <c r="F126">
-        <v>406</v>
+        <v>1126</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766606</t>
+          <t xml:space="preserve">311766629</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">5780012</t>
+          <t xml:space="preserve">7861742</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -6340,11 +6340,11 @@
         </is>
       </c>
       <c r="F127">
-        <v>1126</v>
+        <v>340</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766629</t>
+          <t xml:space="preserve">311766610</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -6381,20 +6381,20 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">7861742</t>
+          <t xml:space="preserve">9049653</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F128">
-        <v>340</v>
+        <v>354</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766610</t>
+          <t xml:space="preserve">311766602</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -6431,25 +6431,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">9049653</t>
+          <t xml:space="preserve">5260044</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F129">
-        <v>354</v>
+        <v>4747</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766602</t>
+          <t xml:space="preserve">311767646</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-06-14</t>
+          <t xml:space="preserve">2034-06-19</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -6486,20 +6486,20 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F130">
-        <v>4747</v>
+        <v>7373</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766871</t>
+          <t xml:space="preserve">311767646</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-06-17</t>
+          <t xml:space="preserve">2034-06-19</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -6536,20 +6536,20 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F131">
-        <v>7373</v>
+        <v>1419</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766871</t>
+          <t xml:space="preserve">311767646</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-06-17</t>
+          <t xml:space="preserve">2034-06-19</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311767653</t>
+          <t xml:space="preserve">311767649</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311767653</t>
+          <t xml:space="preserve">311767649</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -7131,25 +7131,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">309127, 309128, 309129</t>
+          <t xml:space="preserve">5255302</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F143">
-        <v>5924</v>
+        <v>4677</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311783172</t>
+          <t xml:space="preserve">311792061</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-09-06</t>
+          <t xml:space="preserve">2034-10-17</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -7181,25 +7181,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">5255302</t>
+          <t xml:space="preserve">5252364</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F144">
-        <v>4677</v>
+        <v>325</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311792061</t>
+          <t xml:space="preserve">311813574</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-17</t>
+          <t xml:space="preserve">2035-02-24</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F145">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F146">
@@ -7336,15 +7336,15 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F147">
-        <v>325</v>
+        <v>360</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813574</t>
+          <t xml:space="preserve">311813682</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -7386,7 +7386,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F148">
@@ -7436,15 +7436,15 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F149">
-        <v>360</v>
+        <v>1635</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813682</t>
+          <t xml:space="preserve">311813683</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -7481,20 +7481,20 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">5252364</t>
+          <t xml:space="preserve">5774705</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F150">
-        <v>1635</v>
+        <v>408</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813683</t>
+          <t xml:space="preserve">311813570</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">5774705</t>
+          <t xml:space="preserve">5775091</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -7540,11 +7540,11 @@
         </is>
       </c>
       <c r="F151">
-        <v>408</v>
+        <v>1235</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813570</t>
+          <t xml:space="preserve">311813583</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -7581,7 +7581,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">5775091</t>
+          <t xml:space="preserve">5777878</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -7590,16 +7590,16 @@
         </is>
       </c>
       <c r="F152">
-        <v>1235</v>
+        <v>308</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813583</t>
+          <t xml:space="preserve">311813806</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-02-24</t>
+          <t xml:space="preserve">2035-02-25</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777878</t>
+          <t xml:space="preserve">5777949</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -7640,11 +7640,11 @@
         </is>
       </c>
       <c r="F153">
-        <v>308</v>
+        <v>3254</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813806</t>
+          <t xml:space="preserve">311813816</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -7686,15 +7686,15 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F154">
-        <v>3254</v>
+        <v>640</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813816</t>
+          <t xml:space="preserve">311813818</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F155">
@@ -7781,25 +7781,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777949</t>
+          <t xml:space="preserve">737430, 1808354</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F156">
-        <v>640</v>
+        <v>442</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813818</t>
+          <t xml:space="preserve">311814771</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-02-25</t>
+          <t xml:space="preserve">2035-02-28</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814773</t>
+          <t xml:space="preserve">311814771</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -7894,7 +7894,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814773</t>
+          <t xml:space="preserve">311814771</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814773</t>
+          <t xml:space="preserve">311814771</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">5779275</t>
+          <t xml:space="preserve">5252489</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -8890,16 +8890,16 @@
         </is>
       </c>
       <c r="F178">
-        <v>2117</v>
+        <v>984</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831284</t>
+          <t xml:space="preserve">311831852</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-13</t>
+          <t xml:space="preserve">2035-05-14</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -8931,25 +8931,25 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">8540377</t>
+          <t xml:space="preserve">5252489</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F179">
-        <v>9062</v>
+        <v>1460</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831238</t>
+          <t xml:space="preserve">311831852</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-13</t>
+          <t xml:space="preserve">2035-05-14</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -8986,11 +8986,11 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F180">
-        <v>984</v>
+        <v>1034</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
@@ -9036,11 +9036,11 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F181">
-        <v>1460</v>
+        <v>5105</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
@@ -9081,25 +9081,25 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">5252489</t>
+          <t xml:space="preserve">5775088</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F182">
-        <v>1034</v>
+        <v>2142</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831852</t>
+          <t xml:space="preserve">311832051</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-14</t>
+          <t xml:space="preserve">2035-05-15</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -9131,25 +9131,25 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">5252489</t>
+          <t xml:space="preserve">5775088</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F183">
-        <v>5105</v>
+        <v>1062</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831852</t>
+          <t xml:space="preserve">311832051</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-14</t>
+          <t xml:space="preserve">2035-05-15</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -9186,11 +9186,11 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F184">
-        <v>2142</v>
+        <v>2149</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">5775088</t>
+          <t xml:space="preserve">100006578</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -9240,16 +9240,16 @@
         </is>
       </c>
       <c r="F185">
-        <v>1062</v>
+        <v>1429</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311832051</t>
+          <t xml:space="preserve">311868875</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-15</t>
+          <t xml:space="preserve">2035-11-18</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">5775088</t>
+          <t xml:space="preserve">100006578</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -9290,16 +9290,16 @@
         </is>
       </c>
       <c r="F186">
-        <v>2149</v>
+        <v>860</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311832051</t>
+          <t xml:space="preserve">311868877</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-15</t>
+          <t xml:space="preserve">2035-11-18</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -9331,25 +9331,25 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">9058289</t>
+          <t xml:space="preserve">10202622</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F187">
-        <v>610</v>
+        <v>427</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311848623</t>
+          <t xml:space="preserve">311868888</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-12</t>
+          <t xml:space="preserve">2035-11-18</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -9381,25 +9381,25 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">9058289</t>
+          <t xml:space="preserve">5242501</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F188">
-        <v>1113</v>
+        <v>1921</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311848622</t>
+          <t xml:space="preserve">311868868</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-12</t>
+          <t xml:space="preserve">2035-11-18</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -9431,25 +9431,25 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">9058289</t>
+          <t xml:space="preserve">5243868</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F189">
-        <v>604</v>
+        <v>1263</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311848621</t>
+          <t xml:space="preserve">311868866</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-12</t>
+          <t xml:space="preserve">2035-11-18</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -9481,20 +9481,20 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">100006578</t>
+          <t xml:space="preserve">5245639</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F190">
-        <v>1429</v>
+        <v>805</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868875</t>
+          <t xml:space="preserve">311868878</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -9531,20 +9531,20 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve">100006578</t>
+          <t xml:space="preserve">5245639</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F191">
-        <v>860</v>
+        <v>650</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868877</t>
+          <t xml:space="preserve">311868878</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -9581,20 +9581,20 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">10202622</t>
+          <t xml:space="preserve">5245639</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F192">
-        <v>427</v>
+        <v>454</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868888</t>
+          <t xml:space="preserve">311868878</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -9631,20 +9631,20 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t xml:space="preserve">5242501</t>
+          <t xml:space="preserve">5245639</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F193">
-        <v>1921</v>
+        <v>285</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868868</t>
+          <t xml:space="preserve">311868879</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -9681,7 +9681,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t xml:space="preserve">5243868</t>
+          <t xml:space="preserve">5779275</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -9690,11 +9690,11 @@
         </is>
       </c>
       <c r="F194">
-        <v>1263</v>
+        <v>2117</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868866</t>
+          <t xml:space="preserve">311868870</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -9731,20 +9731,20 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t xml:space="preserve">5245639</t>
+          <t xml:space="preserve">9058289</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F195">
-        <v>805</v>
+        <v>610</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868878</t>
+          <t xml:space="preserve">311868873</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -9781,20 +9781,20 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t xml:space="preserve">5245639</t>
+          <t xml:space="preserve">9058289</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F196">
-        <v>650</v>
+        <v>1113</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868878</t>
+          <t xml:space="preserve">311868873</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -9831,20 +9831,20 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t xml:space="preserve">5245639</t>
+          <t xml:space="preserve">9058289</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F197">
-        <v>454</v>
+        <v>604</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868878</t>
+          <t xml:space="preserve">311868873</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -9881,25 +9881,25 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t xml:space="preserve">5245639</t>
+          <t xml:space="preserve">5243526</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F198">
-        <v>285</v>
+        <v>544</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868879</t>
+          <t xml:space="preserve">311871854</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-18</t>
+          <t xml:space="preserve">2035-12-04</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t xml:space="preserve">5243526</t>
+          <t xml:space="preserve">5263733</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -9940,16 +9940,16 @@
         </is>
       </c>
       <c r="F199">
-        <v>544</v>
+        <v>853</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871854</t>
+          <t xml:space="preserve">311875352</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-04</t>
+          <t xml:space="preserve">2036-01-06</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -9986,11 +9986,11 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F200">
-        <v>853</v>
+        <v>1115</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
@@ -10036,11 +10036,11 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F201">
-        <v>1115</v>
+        <v>381</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
@@ -10086,11 +10086,11 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F202">
-        <v>381</v>
+        <v>445</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -10136,11 +10136,11 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F203">
-        <v>445</v>
+        <v>925</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
@@ -10186,11 +10186,11 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F204">
-        <v>925</v>
+        <v>405</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
@@ -10236,11 +10236,11 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F205">
-        <v>405</v>
+        <v>2453</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
@@ -10281,20 +10281,20 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t xml:space="preserve">5263733</t>
+          <t xml:space="preserve">5776345</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F206">
-        <v>2453</v>
+        <v>1081</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875352</t>
+          <t xml:space="preserve">311875335</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -10331,20 +10331,20 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t xml:space="preserve">5776345</t>
+          <t xml:space="preserve">5776859</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F207">
-        <v>1081</v>
+        <v>1615</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875335</t>
+          <t xml:space="preserve">311875334</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t xml:space="preserve">5776859</t>
+          <t xml:space="preserve">5776990</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -10390,11 +10390,11 @@
         </is>
       </c>
       <c r="F208">
-        <v>1615</v>
+        <v>592</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875334</t>
+          <t xml:space="preserve">311875353</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t xml:space="preserve">5776990</t>
+          <t xml:space="preserve">5777609</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -10440,11 +10440,11 @@
         </is>
       </c>
       <c r="F209">
-        <v>592</v>
+        <v>540</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875353</t>
+          <t xml:space="preserve">311875336</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777609</t>
+          <t xml:space="preserve">7681750</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -10490,11 +10490,11 @@
         </is>
       </c>
       <c r="F210">
-        <v>540</v>
+        <v>589</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875336</t>
+          <t xml:space="preserve">311875339</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t xml:space="preserve">7681750</t>
+          <t xml:space="preserve">7791737</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -10540,11 +10540,11 @@
         </is>
       </c>
       <c r="F211">
-        <v>589</v>
+        <v>556</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875339</t>
+          <t xml:space="preserve">311875342</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t xml:space="preserve">7791737</t>
+          <t xml:space="preserve">8052209</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -10590,11 +10590,11 @@
         </is>
       </c>
       <c r="F212">
-        <v>556</v>
+        <v>352</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875342</t>
+          <t xml:space="preserve">311875338</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -10631,7 +10631,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t xml:space="preserve">8052209</t>
+          <t xml:space="preserve">8114886</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -10640,11 +10640,11 @@
         </is>
       </c>
       <c r="F213">
-        <v>352</v>
+        <v>944</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875338</t>
+          <t xml:space="preserve">311875347</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t xml:space="preserve">8114886</t>
+          <t xml:space="preserve">8353545</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -10690,11 +10690,11 @@
         </is>
       </c>
       <c r="F214">
-        <v>944</v>
+        <v>741</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875347</t>
+          <t xml:space="preserve">311875345</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -10731,20 +10731,20 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t xml:space="preserve">8353545</t>
+          <t xml:space="preserve">9058289</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F215">
-        <v>741</v>
+        <v>891</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875345</t>
+          <t xml:space="preserve">311875341</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -10781,20 +10781,20 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t xml:space="preserve">8540377</t>
+          <t xml:space="preserve">9392994</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F216">
-        <v>3204</v>
+        <v>690</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875333</t>
+          <t xml:space="preserve">311875343</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -10831,25 +10831,25 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t xml:space="preserve">9058289</t>
+          <t xml:space="preserve">8540377</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F217">
-        <v>891</v>
+        <v>3204</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875341</t>
+          <t xml:space="preserve">311885684</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-06</t>
+          <t xml:space="preserve">2036-03-05</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -10881,25 +10881,25 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t xml:space="preserve">9392994</t>
+          <t xml:space="preserve">8540377</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F218">
-        <v>690</v>
+        <v>9062</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875343</t>
+          <t xml:space="preserve">311885684</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-06</t>
+          <t xml:space="preserve">2036-03-05</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">

--- a/public/exports/29189854.xlsx
+++ b/public/exports/29189854.xlsx
@@ -91,26 +91,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trondhjemsvej 4</t>
+          <t xml:space="preserve">Flensborgvej 15A</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100053041</t>
+          <t xml:space="preserve">737864, 8331725</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H2">
-        <v>521</v>
+        <v>312</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -211,7 +211,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllemærsk 24</t>
+          <t xml:space="preserve">Hjelmalle 3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">309127, 309128, 309129</t>
+          <t xml:space="preserve">5777400</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -230,7 +230,7 @@
         </is>
       </c>
       <c r="H4">
-        <v>5924</v>
+        <v>3413</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -271,26 +271,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hærvejen 24</t>
+          <t xml:space="preserve">Lendemark 2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6372</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">310466, 310467</t>
+          <t xml:space="preserve">9345287</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H5">
-        <v>1428</v>
+        <v>255</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -331,17 +331,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lergård 88</t>
+          <t xml:space="preserve">Møllevej 2A</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6340</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">311019</t>
+          <t xml:space="preserve">7374968</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -350,7 +350,7 @@
         </is>
       </c>
       <c r="H6">
-        <v>815</v>
+        <v>275</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -451,26 +451,26 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åbovej 12A</t>
+          <t xml:space="preserve">Skrænten 15</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">6372</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">312951, 312952</t>
+          <t xml:space="preserve">9120213</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H8">
-        <v>1169</v>
+        <v>1054</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -511,26 +511,26 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjelmalle 3</t>
+          <t xml:space="preserve">Slogsherredsvej 43</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6372</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777400</t>
+          <t xml:space="preserve">737561, 5238011</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H9">
-        <v>3413</v>
+        <v>252</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -571,26 +571,26 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevej 2A</t>
+          <t xml:space="preserve">Stadionvej 36</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">6340</t>
+          <t xml:space="preserve">6392</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">7374968</t>
+          <t xml:space="preserve">737569, 5248732</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H10">
-        <v>275</v>
+        <v>1777</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -631,26 +631,26 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slogsherredsvej 43</t>
+          <t xml:space="preserve">Trondhjemsvej 4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6372</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">737561, 5238011</t>
+          <t xml:space="preserve">100053041</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H11">
-        <v>252</v>
+        <v>521</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 36</t>
+          <t xml:space="preserve">Tunnelvej 3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">737569, 5248732</t>
+          <t xml:space="preserve">737574, 5248449</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="H12">
-        <v>1777</v>
+        <v>279</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -751,40 +751,40 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tunnelvej 3</t>
+          <t xml:space="preserve">Ringvej 4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">6392</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">737574, 5248449</t>
+          <t xml:space="preserve">8158787</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H13">
-        <v>279</v>
+        <v>413</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200008435</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2018-10-29</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flensborgvej 15A</t>
+          <t xml:space="preserve">Lavgade 52</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -821,30 +821,30 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">737864, 8331725</t>
+          <t xml:space="preserve">5779584</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H14">
-        <v>312</v>
+        <v>1234</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200014490</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-06-03</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skrænten 15</t>
+          <t xml:space="preserve">Sandved 45</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -881,30 +881,30 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">9120213</t>
+          <t xml:space="preserve">5777338</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H15">
-        <v>1054</v>
+        <v>822</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200028497</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-02-24</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -931,40 +931,40 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lendemark 2</t>
+          <t xml:space="preserve">Birkholm 11</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">6372</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">9345287</t>
+          <t xml:space="preserve">737512, 5250365</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H16">
-        <v>255</v>
+        <v>492</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200030398</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-04-16</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ringvej 4</t>
+          <t xml:space="preserve">Hærvejen 24</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">8158787</t>
+          <t xml:space="preserve">310466, 310467</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1010,16 +1010,16 @@
         </is>
       </c>
       <c r="H17">
-        <v>413</v>
+        <v>1428</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">200008435</t>
+          <t xml:space="preserve">310012200</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018-10-29</t>
+          <t xml:space="preserve">2022-11-06</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1051,17 +1051,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lavgade 52</t>
+          <t xml:space="preserve">Plantagevej 8C</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6330</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">5779584</t>
+          <t xml:space="preserve">100049386</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1070,16 +1070,16 @@
         </is>
       </c>
       <c r="H18">
-        <v>1234</v>
+        <v>547</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014490</t>
+          <t xml:space="preserve">311098080</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-03</t>
+          <t xml:space="preserve">2025-03-02</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1111,45 +1111,45 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandved 45</t>
+          <t xml:space="preserve">Åbjerg 8B</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6340</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777338</t>
+          <t xml:space="preserve">5263733</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H19">
-        <v>822</v>
+        <v>534</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">200028497</t>
+          <t xml:space="preserve">311358212</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-24</t>
+          <t xml:space="preserve">2029-02-06</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1171,45 +1171,45 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkholm 11</t>
+          <t xml:space="preserve">Skelbækvej 2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">737512, 5250365</t>
+          <t xml:space="preserve">5777441</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H20">
-        <v>492</v>
+        <v>13747</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">200030398</t>
+          <t xml:space="preserve">311384248</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-04-16</t>
+          <t xml:space="preserve">2029-06-24</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plantagevej 8C</t>
+          <t xml:space="preserve">Valdemarsgade 11</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1241,35 +1241,35 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">100049386</t>
+          <t xml:space="preserve">10006074</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H21">
-        <v>547</v>
+        <v>381</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">311098080</t>
+          <t xml:space="preserve">311385901</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-03-02</t>
+          <t xml:space="preserve">2029-07-02</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1291,35 +1291,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åbjerg 8B</t>
+          <t xml:space="preserve">Skovbrynet 2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">6340</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">5263733</t>
+          <t xml:space="preserve">5256718</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H22">
-        <v>534</v>
+        <v>7580</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">311358212</t>
+          <t xml:space="preserve">311436528</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-06</t>
+          <t xml:space="preserve">2030-05-06</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1351,17 +1351,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skelbækvej 2</t>
+          <t xml:space="preserve">Kirkegade 23</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777441</t>
+          <t xml:space="preserve">5250298</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1370,16 +1370,16 @@
         </is>
       </c>
       <c r="H23">
-        <v>13747</v>
+        <v>626</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311384248</t>
+          <t xml:space="preserve">311498610</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-06-24</t>
+          <t xml:space="preserve">2031-02-25</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1411,35 +1411,35 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdemarsgade 11</t>
+          <t xml:space="preserve">Dronning Margrethes Vej 3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">6330</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">10006074</t>
+          <t xml:space="preserve">5777076</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H24">
-        <v>381</v>
+        <v>452</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311385901</t>
+          <t xml:space="preserve">311522368</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-02</t>
+          <t xml:space="preserve">2031-05-25</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1471,17 +1471,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovbrynet 2</t>
+          <t xml:space="preserve">Tinglev Midt 2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6360</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5256718</t>
+          <t xml:space="preserve">9643472</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1490,16 +1490,16 @@
         </is>
       </c>
       <c r="H25">
-        <v>7580</v>
+        <v>2743</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311436528</t>
+          <t xml:space="preserve">311522375</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-05-06</t>
+          <t xml:space="preserve">2031-05-25</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1531,35 +1531,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 23</t>
+          <t xml:space="preserve">Tinglev Midt 4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6360</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5250298</t>
+          <t xml:space="preserve">9643472</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H26">
-        <v>626</v>
+        <v>1267</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311498610</t>
+          <t xml:space="preserve">311522371</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-25</t>
+          <t xml:space="preserve">2031-05-25</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1591,35 +1591,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronning Margrethes Vej 3</t>
+          <t xml:space="preserve">Grønnevej 32</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6360</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777076</t>
+          <t xml:space="preserve">9643472</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H27">
-        <v>452</v>
+        <v>847</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311522368</t>
+          <t xml:space="preserve">311578480</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-25</t>
+          <t xml:space="preserve">2032-02-13</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1666,20 +1666,20 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H28">
-        <v>2743</v>
+        <v>847</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311522375</t>
+          <t xml:space="preserve">311578481</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-25</t>
+          <t xml:space="preserve">2032-02-13</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tinglev Midt 4</t>
+          <t xml:space="preserve">Grønnevej 32</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1726,20 +1726,20 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H29">
-        <v>1267</v>
+        <v>602</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311522371</t>
+          <t xml:space="preserve">311578773</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-25</t>
+          <t xml:space="preserve">2032-02-15</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -1771,17 +1771,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnevej 32</t>
+          <t xml:space="preserve">Østermarkvej 1P</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">6360</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">9643472</t>
+          <t xml:space="preserve">8073695</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1790,16 +1790,16 @@
         </is>
       </c>
       <c r="H30">
-        <v>847</v>
+        <v>555</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311578480</t>
+          <t xml:space="preserve">311601866</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-13</t>
+          <t xml:space="preserve">2032-05-20</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -1831,35 +1831,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tinglev Midt 2</t>
+          <t xml:space="preserve">Kalveknækket 47</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">6360</t>
+          <t xml:space="preserve">6340</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">9643472</t>
+          <t xml:space="preserve">5262648</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H31">
-        <v>847</v>
+        <v>2330</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311578481</t>
+          <t xml:space="preserve">311644250</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-13</t>
+          <t xml:space="preserve">2032-11-22</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -1891,35 +1891,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnevej 32</t>
+          <t xml:space="preserve">Molevej 18A</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">6360</t>
+          <t xml:space="preserve">6340</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">9643472</t>
+          <t xml:space="preserve">5262575</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H32">
-        <v>602</v>
+        <v>336</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311578773</t>
+          <t xml:space="preserve">311650394</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-15</t>
+          <t xml:space="preserve">2032-12-20</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -1951,35 +1951,35 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østermarkvej 1P</t>
+          <t xml:space="preserve">Smedefod 4B</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6392</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">8073695</t>
+          <t xml:space="preserve">5248731</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H33">
-        <v>555</v>
+        <v>316</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601866</t>
+          <t xml:space="preserve">311650397</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-20</t>
+          <t xml:space="preserve">2032-12-20</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalveknækket 47</t>
+          <t xml:space="preserve">Åbovej 12A</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">6340</t>
+          <t xml:space="preserve">6372</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">5262648</t>
+          <t xml:space="preserve">312951, 312952</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2030,16 +2030,16 @@
         </is>
       </c>
       <c r="H34">
-        <v>2330</v>
+        <v>1169</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644250</t>
+          <t xml:space="preserve">311650395</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-22</t>
+          <t xml:space="preserve">2032-12-20</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2071,17 +2071,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedefod 4B</t>
+          <t xml:space="preserve">Skolegade 2</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">6392</t>
+          <t xml:space="preserve">6340</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">5248731</t>
+          <t xml:space="preserve">100044523</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2090,16 +2090,16 @@
         </is>
       </c>
       <c r="H35">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650397</t>
+          <t xml:space="preserve">311653972</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-20</t>
+          <t xml:space="preserve">2033-01-13</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2131,35 +2131,35 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molevej 18A</t>
+          <t xml:space="preserve">Skovbrynet 4</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">6340</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">5262575</t>
+          <t xml:space="preserve">5256718</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="H36">
-        <v>336</v>
+        <v>778</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650394</t>
+          <t xml:space="preserve">311654332</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-20</t>
+          <t xml:space="preserve">2033-01-16</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2191,35 +2191,35 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 2</t>
+          <t xml:space="preserve">Skovbrynet 4</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">6340</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">100044523</t>
+          <t xml:space="preserve">5256718</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="H37">
-        <v>334</v>
+        <v>665</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311653972</t>
+          <t xml:space="preserve">311654333</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-13</t>
+          <t xml:space="preserve">2033-01-16</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2251,35 +2251,35 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovbrynet 4</t>
+          <t xml:space="preserve">Kalveknækket 45A</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6340</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">5256718</t>
+          <t xml:space="preserve">5262778</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H38">
-        <v>778</v>
+        <v>558</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654332</t>
+          <t xml:space="preserve">311654619</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-16</t>
+          <t xml:space="preserve">2033-01-18</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2311,35 +2311,35 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovbrynet 4</t>
+          <t xml:space="preserve">Flensborgvej 9B</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6340</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">5256718</t>
+          <t xml:space="preserve">5263423</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H39">
-        <v>665</v>
+        <v>348</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654333</t>
+          <t xml:space="preserve">311661161</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-16</t>
+          <t xml:space="preserve">2033-02-20</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2371,35 +2371,35 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalveknækket 45A</t>
+          <t xml:space="preserve">Mads Clausens Vej 130</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">6340</t>
+          <t xml:space="preserve">6360</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">5262778</t>
+          <t xml:space="preserve">5243879</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H40">
-        <v>558</v>
+        <v>814</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654619</t>
+          <t xml:space="preserve">311661163</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-18</t>
+          <t xml:space="preserve">2033-02-20</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2431,30 +2431,30 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tværvejen 4</t>
+          <t xml:space="preserve">Smedefod 10A</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">6360</t>
+          <t xml:space="preserve">6392</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">5242741</t>
+          <t xml:space="preserve">5248692</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H41">
-        <v>338</v>
+        <v>3970</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661169</t>
+          <t xml:space="preserve">311661158</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mads Clausens Vej 130</t>
+          <t xml:space="preserve">Tværvejen 4</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">5243879</t>
+          <t xml:space="preserve">5242741</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2510,11 +2510,11 @@
         </is>
       </c>
       <c r="H42">
-        <v>814</v>
+        <v>338</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661163</t>
+          <t xml:space="preserve">311661169</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2551,35 +2551,35 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedefod 10A</t>
+          <t xml:space="preserve">Hovedgaden 82</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">6392</t>
+          <t xml:space="preserve">6360</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">5248692</t>
+          <t xml:space="preserve">5242835</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H43">
-        <v>3970</v>
+        <v>357</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661158</t>
+          <t xml:space="preserve">311661649</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-20</t>
+          <t xml:space="preserve">2033-02-22</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2611,17 +2611,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flensborgvej 9B</t>
+          <t xml:space="preserve">Nørrekær 15</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">6340</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">5263423</t>
+          <t xml:space="preserve">9073631</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2630,16 +2630,16 @@
         </is>
       </c>
       <c r="H44">
-        <v>348</v>
+        <v>3104</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661161</t>
+          <t xml:space="preserve">311661636</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-20</t>
+          <t xml:space="preserve">2033-02-22</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2671,17 +2671,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åbovej 27A</t>
+          <t xml:space="preserve">Skolegade 12A</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">6372</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">5235664</t>
+          <t xml:space="preserve">5270230</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2690,11 +2690,11 @@
         </is>
       </c>
       <c r="H45">
-        <v>319</v>
+        <v>1798</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661637</t>
+          <t xml:space="preserve">311661646</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2731,30 +2731,30 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 82</t>
+          <t xml:space="preserve">Skolegade 12B</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">6360</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">5242835</t>
+          <t xml:space="preserve">5270230</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H46">
-        <v>357</v>
+        <v>516</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661649</t>
+          <t xml:space="preserve">311661646</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 12A</t>
+          <t xml:space="preserve">Skolegade 12C</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2806,15 +2806,15 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H47">
-        <v>1798</v>
+        <v>409</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661646</t>
+          <t xml:space="preserve">311661642</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2851,30 +2851,30 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 12B</t>
+          <t xml:space="preserve">Åbovej 27A</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6372</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">5270230</t>
+          <t xml:space="preserve">5235664</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H48">
-        <v>516</v>
+        <v>319</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661646</t>
+          <t xml:space="preserve">311661637</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2911,35 +2911,35 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 12C</t>
+          <t xml:space="preserve">Sønderskovvej 25</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6360</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">5270230</t>
+          <t xml:space="preserve">9734086</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H49">
-        <v>409</v>
+        <v>829</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661642</t>
+          <t xml:space="preserve">311661950</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-22</t>
+          <t xml:space="preserve">2033-02-23</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -2971,35 +2971,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrekær 15</t>
+          <t xml:space="preserve">Sønderskovvej 27</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6360</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">9073631</t>
+          <t xml:space="preserve">9734086</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H50">
-        <v>3104</v>
+        <v>364</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661636</t>
+          <t xml:space="preserve">311661950</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-22</t>
+          <t xml:space="preserve">2033-02-23</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3031,17 +3031,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderskovvej 25</t>
+          <t xml:space="preserve">Engløkke 30</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">6360</t>
+          <t xml:space="preserve">6372</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">9734086</t>
+          <t xml:space="preserve">5235995</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3050,16 +3050,16 @@
         </is>
       </c>
       <c r="H51">
-        <v>829</v>
+        <v>4022</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661951</t>
+          <t xml:space="preserve">311667969</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-23</t>
+          <t xml:space="preserve">2033-03-21</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3091,35 +3091,35 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderskovvej 27</t>
+          <t xml:space="preserve">Kliplev Hovedgade 6A</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">6360</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">9734086</t>
+          <t xml:space="preserve">9319699</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H52">
-        <v>364</v>
+        <v>1216</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661951</t>
+          <t xml:space="preserve">311667988</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-23</t>
+          <t xml:space="preserve">2033-03-21</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3151,30 +3151,30 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engløkke 30</t>
+          <t xml:space="preserve">Kliplev Hovedgade 6B</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">6372</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">5235995</t>
+          <t xml:space="preserve">9319699</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H53">
-        <v>4022</v>
+        <v>524</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311667969</t>
+          <t xml:space="preserve">311667989</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3271,17 +3271,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kliplev Hovedgade 6A</t>
+          <t xml:space="preserve">Østermarkvej 1A</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">9319699</t>
+          <t xml:space="preserve">8073695</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3290,16 +3290,16 @@
         </is>
       </c>
       <c r="H55">
-        <v>1216</v>
+        <v>406</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311667988</t>
+          <t xml:space="preserve">311668436</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-21</t>
+          <t xml:space="preserve">2033-03-22</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3331,17 +3331,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kliplev Hovedgade 6B</t>
+          <t xml:space="preserve">Østermarkvej 1B</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">9319699</t>
+          <t xml:space="preserve">8073695</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3350,16 +3350,16 @@
         </is>
       </c>
       <c r="H56">
-        <v>524</v>
+        <v>935</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311668057</t>
+          <t xml:space="preserve">311668438</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-21</t>
+          <t xml:space="preserve">2033-03-22</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3391,17 +3391,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østermarkvej 1A</t>
+          <t xml:space="preserve">Bytoften 13</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">8073695</t>
+          <t xml:space="preserve">5274226</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3410,16 +3410,16 @@
         </is>
       </c>
       <c r="H57">
-        <v>406</v>
+        <v>854</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311668436</t>
+          <t xml:space="preserve">311670155</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-22</t>
+          <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3451,35 +3451,35 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østermarkvej 1B</t>
+          <t xml:space="preserve">Hovedgaden 78</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6360</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">8073695</t>
+          <t xml:space="preserve">5242501</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H58">
-        <v>935</v>
+        <v>1466</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311668438</t>
+          <t xml:space="preserve">311670158</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-22</t>
+          <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3526,11 +3526,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H59">
-        <v>1466</v>
+        <v>1439</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3586,11 +3586,11 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H60">
-        <v>1439</v>
+        <v>1390</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3631,30 +3631,30 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørreagervej 45</t>
+          <t xml:space="preserve">Klostervang 46</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">6360</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">5242501</t>
+          <t xml:space="preserve">5270632</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H61">
-        <v>3702</v>
+        <v>608</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670158</t>
+          <t xml:space="preserve">311670156</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3691,30 +3691,30 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 78</t>
+          <t xml:space="preserve">Kobbermøllevej 50A</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">6360</t>
+          <t xml:space="preserve">6340</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">5242501</t>
+          <t xml:space="preserve">8162582</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H62">
-        <v>1390</v>
+        <v>1072</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670158</t>
+          <t xml:space="preserve">311670165</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3751,30 +3751,30 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostervang 46</t>
+          <t xml:space="preserve">Kobbermøllevej 50B</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6340</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">5270632</t>
+          <t xml:space="preserve">8162582</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H63">
-        <v>608</v>
+        <v>408</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670156</t>
+          <t xml:space="preserve">311670164</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3811,30 +3811,30 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bytoften 13</t>
+          <t xml:space="preserve">Kobbermøllevej 50C</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6340</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5274226</t>
+          <t xml:space="preserve">8162582</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H64">
-        <v>854</v>
+        <v>408</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670155</t>
+          <t xml:space="preserve">311670164</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3871,30 +3871,30 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Varnæs Kirkevej 15</t>
+          <t xml:space="preserve">Kobbermøllevej 50D</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6340</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">5274894</t>
+          <t xml:space="preserve">8162582</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H65">
-        <v>2071</v>
+        <v>408</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670153</t>
+          <t xml:space="preserve">311670164</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kobbermøllevej 50A</t>
+          <t xml:space="preserve">Kobbermøllevej 50E</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3946,15 +3946,15 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="H66">
-        <v>1072</v>
+        <v>408</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670161</t>
+          <t xml:space="preserve">311670164</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3991,30 +3991,30 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kobbermøllevej 50B</t>
+          <t xml:space="preserve">Nørreagervej 45</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">6340</t>
+          <t xml:space="preserve">6360</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">8162582</t>
+          <t xml:space="preserve">5242501</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H67">
-        <v>408</v>
+        <v>3702</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670161</t>
+          <t xml:space="preserve">311670158</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4051,30 +4051,30 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kobbermøllevej 50C</t>
+          <t xml:space="preserve">Ravsted Skolegade 16</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">6340</t>
+          <t xml:space="preserve">6372</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">8162582</t>
+          <t xml:space="preserve">9345395</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H68">
-        <v>408</v>
+        <v>267</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670161</t>
+          <t xml:space="preserve">311670238</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4111,30 +4111,30 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kobbermøllevej 50D</t>
+          <t xml:space="preserve">Ravsted Skolegade 18</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">6340</t>
+          <t xml:space="preserve">6372</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">8162582</t>
+          <t xml:space="preserve">9345395</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H69">
-        <v>408</v>
+        <v>2157</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670161</t>
+          <t xml:space="preserve">311670236</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4171,30 +4171,30 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kobbermøllevej 50E</t>
+          <t xml:space="preserve">Varnæs Kirkevej 15</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">6340</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">8162582</t>
+          <t xml:space="preserve">5274894</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H70">
-        <v>408</v>
+        <v>2071</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670161</t>
+          <t xml:space="preserve">311670153</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4231,17 +4231,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravsted Skolegade 18</t>
+          <t xml:space="preserve">Gammel Søndergade 20A</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">6372</t>
+          <t xml:space="preserve">6392</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">9345395</t>
+          <t xml:space="preserve">5248471</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4250,16 +4250,16 @@
         </is>
       </c>
       <c r="H71">
-        <v>2157</v>
+        <v>358</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670236</t>
+          <t xml:space="preserve">311670600</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-29</t>
+          <t xml:space="preserve">2033-03-30</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravsted Skolegade 16</t>
+          <t xml:space="preserve">Gammel Søndergade 20A</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">6372</t>
+          <t xml:space="preserve">6392</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">9345395</t>
+          <t xml:space="preserve">5248471</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4310,16 +4310,16 @@
         </is>
       </c>
       <c r="H72">
-        <v>267</v>
+        <v>862</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670238</t>
+          <t xml:space="preserve">311670599</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-29</t>
+          <t xml:space="preserve">2033-03-30</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Søndergade 20A</t>
+          <t xml:space="preserve">Gammel Søndergade 20L</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4361,20 +4361,20 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">5248471</t>
+          <t xml:space="preserve">8040385</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H73">
-        <v>358</v>
+        <v>470</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670600</t>
+          <t xml:space="preserve">311670603</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4411,35 +4411,35 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Søndergade 20A</t>
+          <t xml:space="preserve">Slogsherredsvej 27</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">6392</t>
+          <t xml:space="preserve">6372</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">5248471</t>
+          <t xml:space="preserve">9120321</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H74">
-        <v>862</v>
+        <v>2095</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670599</t>
+          <t xml:space="preserve">311673018</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-30</t>
+          <t xml:space="preserve">2033-04-12</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4471,17 +4471,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Søndergade 20L</t>
+          <t xml:space="preserve">Slogsherredsvej 27</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">6392</t>
+          <t xml:space="preserve">6372</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040385</t>
+          <t xml:space="preserve">9120321</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4490,16 +4490,16 @@
         </is>
       </c>
       <c r="H75">
-        <v>470</v>
+        <v>806</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670603</t>
+          <t xml:space="preserve">311673018</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-30</t>
+          <t xml:space="preserve">2033-04-12</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4546,11 +4546,11 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H76">
-        <v>2095</v>
+        <v>2646</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -4591,35 +4591,35 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slogsherredsvej 27</t>
+          <t xml:space="preserve">Bovvej 2A</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">6372</t>
+          <t xml:space="preserve">6330</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">9120321</t>
+          <t xml:space="preserve">9069219</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H77">
-        <v>806</v>
+        <v>314</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311673018</t>
+          <t xml:space="preserve">311678991</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-12</t>
+          <t xml:space="preserve">2033-05-08</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -4651,35 +4651,35 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slogsherredsvej 27</t>
+          <t xml:space="preserve">Bovvej 2B</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">6372</t>
+          <t xml:space="preserve">6330</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">9120321</t>
+          <t xml:space="preserve">9069219</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H78">
-        <v>2646</v>
+        <v>510</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311673018</t>
+          <t xml:space="preserve">311678991</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-12</t>
+          <t xml:space="preserve">2033-05-08</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bovvej 4</t>
+          <t xml:space="preserve">Bovvej 2B</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4721,20 +4721,20 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">5260034</t>
+          <t xml:space="preserve">9069219</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H79">
-        <v>1438</v>
+        <v>268</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311679002</t>
+          <t xml:space="preserve">311678991</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bovvej 2A</t>
+          <t xml:space="preserve">Bovvej 4</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4781,20 +4781,20 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">9069219</t>
+          <t xml:space="preserve">5260034</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H80">
-        <v>314</v>
+        <v>1438</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311678991</t>
+          <t xml:space="preserve">311679002</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bovvej 2B</t>
+          <t xml:space="preserve">Jernbanegade 14</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4841,25 +4841,25 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">9069219</t>
+          <t xml:space="preserve">5259724</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H81">
-        <v>510</v>
+        <v>438</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311678991</t>
+          <t xml:space="preserve">311680033</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-08</t>
+          <t xml:space="preserve">2033-05-11</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bovvej 2B</t>
+          <t xml:space="preserve">Jernbanegade 36A</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4901,25 +4901,25 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">9069219</t>
+          <t xml:space="preserve">5260026</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H82">
-        <v>268</v>
+        <v>415</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311678991</t>
+          <t xml:space="preserve">311680035</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-08</t>
+          <t xml:space="preserve">2033-05-11</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanegade 14</t>
+          <t xml:space="preserve">Padborgvej 20A</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">5259724</t>
+          <t xml:space="preserve">9410204</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4970,16 +4970,16 @@
         </is>
       </c>
       <c r="H83">
-        <v>438</v>
+        <v>1971</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311680033</t>
+          <t xml:space="preserve">311691896</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-11</t>
+          <t xml:space="preserve">2033-06-30</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanegade 36A</t>
+          <t xml:space="preserve">Padborgvej 20B</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5021,25 +5021,25 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">5260026</t>
+          <t xml:space="preserve">9410204</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H84">
-        <v>415</v>
+        <v>1232</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311680035</t>
+          <t xml:space="preserve">311691894</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-11</t>
+          <t xml:space="preserve">2033-06-30</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Padborgvej 20A</t>
+          <t xml:space="preserve">Padborgvej 20C</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5086,15 +5086,15 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H85">
-        <v>1971</v>
+        <v>451</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311691896</t>
+          <t xml:space="preserve">311691894</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Padborgvej 20B</t>
+          <t xml:space="preserve">Padborgvej 20D</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5146,11 +5146,11 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H86">
-        <v>1232</v>
+        <v>573</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Padborgvej 20C</t>
+          <t xml:space="preserve">Plantagevej 2B</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5201,25 +5201,25 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">9410204</t>
+          <t xml:space="preserve">5260531</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H87">
-        <v>451</v>
+        <v>1842</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311691894</t>
+          <t xml:space="preserve">311696895</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-30</t>
+          <t xml:space="preserve">2033-07-27</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Padborgvej 20D</t>
+          <t xml:space="preserve">Kempesteens Vej 70</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5261,25 +5261,25 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">9410204</t>
+          <t xml:space="preserve">5260533</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H88">
-        <v>573</v>
+        <v>492</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311691894</t>
+          <t xml:space="preserve">311706365</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-30</t>
+          <t xml:space="preserve">2033-09-11</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5311,17 +5311,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plantagevej 2B</t>
+          <t xml:space="preserve">Lergård 88</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">6330</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">5260531</t>
+          <t xml:space="preserve">311019</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5330,16 +5330,16 @@
         </is>
       </c>
       <c r="H89">
-        <v>1842</v>
+        <v>815</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311696895</t>
+          <t xml:space="preserve">311717620</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-07-27</t>
+          <t xml:space="preserve">2033-10-25</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5371,17 +5371,17 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kempesteens Vej 70</t>
+          <t xml:space="preserve">Funkevej 9A</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">6330</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">5260533</t>
+          <t xml:space="preserve">5254271</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5390,16 +5390,16 @@
         </is>
       </c>
       <c r="H90">
-        <v>492</v>
+        <v>415</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706365</t>
+          <t xml:space="preserve">311763725</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-11</t>
+          <t xml:space="preserve">2034-06-03</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5446,15 +5446,15 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H91">
-        <v>415</v>
+        <v>1536</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763725</t>
+          <t xml:space="preserve">311763724</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5506,15 +5506,15 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H92">
-        <v>1536</v>
+        <v>452</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763724</t>
+          <t xml:space="preserve">311763725</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5551,17 +5551,17 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Funkevej 9A</t>
+          <t xml:space="preserve">Gasværksvej 20</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">5254271</t>
+          <t xml:space="preserve">5775323</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5570,11 +5570,11 @@
         </is>
       </c>
       <c r="H93">
-        <v>452</v>
+        <v>2574</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763725</t>
+          <t xml:space="preserve">311763728</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5611,30 +5611,30 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 40C</t>
+          <t xml:space="preserve">Gråstenvej 1</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">5254347</t>
+          <t xml:space="preserve">7747263</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H94">
-        <v>520</v>
+        <v>2087</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763739</t>
+          <t xml:space="preserve">311763695</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -5671,17 +5671,17 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 20</t>
+          <t xml:space="preserve">Gråstenvej 12</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">5255563</t>
+          <t xml:space="preserve">9303236</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5690,11 +5690,11 @@
         </is>
       </c>
       <c r="H95">
-        <v>868</v>
+        <v>677</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763694</t>
+          <t xml:space="preserve">311763696</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5791,30 +5791,30 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvej 10</t>
+          <t xml:space="preserve">Lavgade 30</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">6340</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">5268254</t>
+          <t xml:space="preserve">5775595</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H97">
-        <v>1015</v>
+        <v>2589</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763726</t>
+          <t xml:space="preserve">311763897</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -5851,30 +5851,30 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvej 10</t>
+          <t xml:space="preserve">Nygade 20</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">6340</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">5268269</t>
+          <t xml:space="preserve">5775595</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H98">
-        <v>262</v>
+        <v>3338</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763735</t>
+          <t xml:space="preserve">311763900</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -5921,20 +5921,20 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">5268269</t>
+          <t xml:space="preserve">5268254</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H99">
-        <v>258</v>
+        <v>1015</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763735</t>
+          <t xml:space="preserve">311763726</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -5971,17 +5971,17 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gasværksvej 20</t>
+          <t xml:space="preserve">Strandvej 10</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6340</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">5775323</t>
+          <t xml:space="preserve">5268269</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -5990,11 +5990,11 @@
         </is>
       </c>
       <c r="H100">
-        <v>2574</v>
+        <v>262</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763728</t>
+          <t xml:space="preserve">311763735</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6031,30 +6031,30 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lavgade 30</t>
+          <t xml:space="preserve">Strandvej 10</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6340</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">5775595</t>
+          <t xml:space="preserve">5268269</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H101">
-        <v>2589</v>
+        <v>258</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763897</t>
+          <t xml:space="preserve">311763735</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6091,30 +6091,30 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 20</t>
+          <t xml:space="preserve">Vestergade 20</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">5775595</t>
+          <t xml:space="preserve">5255563</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H102">
-        <v>3338</v>
+        <v>868</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763900</t>
+          <t xml:space="preserve">311763694</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -6151,30 +6151,30 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gråstenvej 1</t>
+          <t xml:space="preserve">Østergade 40C</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">7747263</t>
+          <t xml:space="preserve">5254347</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H103">
-        <v>2087</v>
+        <v>520</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763695</t>
+          <t xml:space="preserve">311763739</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6211,17 +6211,17 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gråstenvej 12</t>
+          <t xml:space="preserve">Birkholm 7</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">9303236</t>
+          <t xml:space="preserve">5250365</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6230,16 +6230,16 @@
         </is>
       </c>
       <c r="H104">
-        <v>677</v>
+        <v>4382</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763696</t>
+          <t xml:space="preserve">311764478</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-06-03</t>
+          <t xml:space="preserve">2034-06-06</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovslundvej 12</t>
+          <t xml:space="preserve">Birkholm 7</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6281,20 +6281,20 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">5247379</t>
+          <t xml:space="preserve">5250365</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H105">
-        <v>564</v>
+        <v>1154</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311764473</t>
+          <t xml:space="preserve">311764478</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovslundvej 12</t>
+          <t xml:space="preserve">Birkholm 7</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6341,20 +6341,20 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">5247379</t>
+          <t xml:space="preserve">5250365</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H106">
-        <v>1639</v>
+        <v>1483</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311764473</t>
+          <t xml:space="preserve">311764476</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkholm 7</t>
+          <t xml:space="preserve">Genner Bygade 3</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">5250365</t>
+          <t xml:space="preserve">8662006</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -6410,11 +6410,11 @@
         </is>
       </c>
       <c r="H107">
-        <v>4382</v>
+        <v>1769</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311764478</t>
+          <t xml:space="preserve">311764471</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkholm 7</t>
+          <t xml:space="preserve">Genner Bygade 3</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">5250365</t>
+          <t xml:space="preserve">8662006</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -6470,11 +6470,11 @@
         </is>
       </c>
       <c r="H108">
-        <v>1154</v>
+        <v>1063</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311764478</t>
+          <t xml:space="preserve">311764471</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkholm 7</t>
+          <t xml:space="preserve">Genner Bygade 3</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -6521,20 +6521,20 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">5250365</t>
+          <t xml:space="preserve">8662006</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H109">
-        <v>1483</v>
+        <v>275</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311764476</t>
+          <t xml:space="preserve">311764471</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Genner Bygade 3</t>
+          <t xml:space="preserve">Hovslundvej 12</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">8662006</t>
+          <t xml:space="preserve">5247379</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -6590,11 +6590,11 @@
         </is>
       </c>
       <c r="H110">
-        <v>1769</v>
+        <v>564</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311764471</t>
+          <t xml:space="preserve">311764474</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Genner Bygade 3</t>
+          <t xml:space="preserve">Hovslundvej 12</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">8662006</t>
+          <t xml:space="preserve">5247379</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -6650,11 +6650,11 @@
         </is>
       </c>
       <c r="H111">
-        <v>1063</v>
+        <v>1639</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311764471</t>
+          <t xml:space="preserve">311764474</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Genner Bygade 3</t>
+          <t xml:space="preserve">Østergade 40B</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -6701,25 +6701,25 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">8662006</t>
+          <t xml:space="preserve">5254347</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H112">
-        <v>275</v>
+        <v>326</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311764471</t>
+          <t xml:space="preserve">311764844</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-06-06</t>
+          <t xml:space="preserve">2034-06-07</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -6766,11 +6766,11 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H113">
-        <v>326</v>
+        <v>1272</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -6811,35 +6811,35 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 40B</t>
+          <t xml:space="preserve">Bjerggade 3</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">5254347</t>
+          <t xml:space="preserve">5777914</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H114">
-        <v>1272</v>
+        <v>406</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311764844</t>
+          <t xml:space="preserve">311766606</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-06-07</t>
+          <t xml:space="preserve">2034-06-14</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -6871,17 +6871,17 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 61</t>
+          <t xml:space="preserve">Borgmesterløkken 35</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">5254851</t>
+          <t xml:space="preserve">7861742</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -6890,11 +6890,11 @@
         </is>
       </c>
       <c r="H115">
-        <v>1054</v>
+        <v>340</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766708</t>
+          <t xml:space="preserve">311766610</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -6931,30 +6931,30 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 63</t>
+          <t xml:space="preserve">Haderslevvej 1</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">5254851</t>
+          <t xml:space="preserve">5780012</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H116">
-        <v>1406</v>
+        <v>1126</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766710</t>
+          <t xml:space="preserve">311766629</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -6991,30 +6991,30 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 24A</t>
+          <t xml:space="preserve">Hjelmalle 3</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">5255997</t>
+          <t xml:space="preserve">5777400</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H117">
-        <v>293</v>
+        <v>2585</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766615</t>
+          <t xml:space="preserve">311766632</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7051,30 +7051,30 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovbrynet 2</t>
+          <t xml:space="preserve">Hjelmalle 3</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">5256718</t>
+          <t xml:space="preserve">5777400</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H118">
-        <v>1396</v>
+        <v>1285</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766630</t>
+          <t xml:space="preserve">311766632</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7111,30 +7111,30 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovbrynet 2</t>
+          <t xml:space="preserve">Hjelmalle 3</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">5256718</t>
+          <t xml:space="preserve">5777400</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H119">
-        <v>1087</v>
+        <v>5606</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766630</t>
+          <t xml:space="preserve">311766632</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7171,30 +7171,30 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovbrynet 2</t>
+          <t xml:space="preserve">Plantagevej 4</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6330</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">5256718</t>
+          <t xml:space="preserve">5260532</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H120">
-        <v>619</v>
+        <v>4077</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766630</t>
+          <t xml:space="preserve">311766620</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -7231,30 +7231,30 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plantagevej 4</t>
+          <t xml:space="preserve">Skovbrynet 2</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">6330</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">5260532</t>
+          <t xml:space="preserve">5256718</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H121">
-        <v>4077</v>
+        <v>1396</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766620</t>
+          <t xml:space="preserve">311766630</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -7291,30 +7291,30 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjelmalle 3</t>
+          <t xml:space="preserve">Skovbrynet 2</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777400</t>
+          <t xml:space="preserve">5256718</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
       <c r="H122">
-        <v>2585</v>
+        <v>1087</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766632</t>
+          <t xml:space="preserve">311766630</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -7351,17 +7351,17 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjelmalle 3</t>
+          <t xml:space="preserve">Skovbrynet 2</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777400</t>
+          <t xml:space="preserve">5256718</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -7370,11 +7370,11 @@
         </is>
       </c>
       <c r="H123">
-        <v>1285</v>
+        <v>619</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766632</t>
+          <t xml:space="preserve">311766630</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -7411,7 +7411,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjelmalle 3</t>
+          <t xml:space="preserve">Sønderborgvej 137</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7421,20 +7421,20 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777400</t>
+          <t xml:space="preserve">9049653</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H124">
-        <v>5606</v>
+        <v>354</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766632</t>
+          <t xml:space="preserve">311766602</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -7471,17 +7471,17 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjerggade 3</t>
+          <t xml:space="preserve">Vestergade 24A</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777914</t>
+          <t xml:space="preserve">5255997</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -7490,11 +7490,11 @@
         </is>
       </c>
       <c r="H125">
-        <v>406</v>
+        <v>293</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766606</t>
+          <t xml:space="preserve">311766615</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -7531,17 +7531,17 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Haderslevvej 1</t>
+          <t xml:space="preserve">Østergade 61</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">5780012</t>
+          <t xml:space="preserve">5254851</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -7550,11 +7550,11 @@
         </is>
       </c>
       <c r="H126">
-        <v>1126</v>
+        <v>1054</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766629</t>
+          <t xml:space="preserve">311766708</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -7591,30 +7591,30 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgmesterløkken 35</t>
+          <t xml:space="preserve">Østergade 63</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">7861742</t>
+          <t xml:space="preserve">5254851</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H127">
-        <v>340</v>
+        <v>1406</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766610</t>
+          <t xml:space="preserve">311766710</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderborgvej 137</t>
+          <t xml:space="preserve">Kallemosen 18</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -7661,25 +7661,25 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">9049653</t>
+          <t xml:space="preserve">5777160</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H128">
-        <v>354</v>
+        <v>372</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766602</t>
+          <t xml:space="preserve">311767653</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-06-14</t>
+          <t xml:space="preserve">2034-06-19</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -7711,30 +7711,30 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 2</t>
+          <t xml:space="preserve">Kallemosen 20</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">6330</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">5260044</t>
+          <t xml:space="preserve">5777160</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H129">
-        <v>4747</v>
+        <v>3627</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311767646</t>
+          <t xml:space="preserve">311767653</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Padborgvej 55A</t>
+          <t xml:space="preserve">Kirkevej 2</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -7786,11 +7786,11 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H130">
-        <v>7373</v>
+        <v>4747</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Padborgvej 55B</t>
+          <t xml:space="preserve">Padborgvej 55A</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -7846,11 +7846,11 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H131">
-        <v>1419</v>
+        <v>7373</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -7891,30 +7891,30 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kallemosen 20</t>
+          <t xml:space="preserve">Padborgvej 55B</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6330</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777160</t>
+          <t xml:space="preserve">5260044</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H132">
-        <v>3627</v>
+        <v>1419</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311767653</t>
+          <t xml:space="preserve">311767646</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -7951,17 +7951,17 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kallemosen 18</t>
+          <t xml:space="preserve">Skovbrynet 10</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777160</t>
+          <t xml:space="preserve">5256718</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -7970,16 +7970,16 @@
         </is>
       </c>
       <c r="H133">
-        <v>372</v>
+        <v>2110</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311767653</t>
+          <t xml:space="preserve">311767974</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-06-19</t>
+          <t xml:space="preserve">2034-06-20</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -8026,15 +8026,15 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H134">
-        <v>2110</v>
+        <v>470</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311767974</t>
+          <t xml:space="preserve">311767973</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -8131,35 +8131,35 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovbrynet 10</t>
+          <t xml:space="preserve">Pilemosen 21</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">5256718</t>
+          <t xml:space="preserve">5777457</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H136">
-        <v>470</v>
+        <v>1635</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311767973</t>
+          <t xml:space="preserve">311768984</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-06-20</t>
+          <t xml:space="preserve">2034-06-25</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pilemosen 21</t>
+          <t xml:space="preserve">Sønderborgvej 137</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8201,25 +8201,25 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777457</t>
+          <t xml:space="preserve">9049653</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H137">
-        <v>1635</v>
+        <v>542</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311768984</t>
+          <t xml:space="preserve">311770633</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-06-25</t>
+          <t xml:space="preserve">2034-07-02</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -8266,15 +8266,15 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H138">
-        <v>542</v>
+        <v>6116</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311770633</t>
+          <t xml:space="preserve">311770634</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -8326,11 +8326,11 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H139">
-        <v>6116</v>
+        <v>664</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
@@ -8371,35 +8371,35 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderborgvej 137</t>
+          <t xml:space="preserve">Slogsherredsvej 41</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6372</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">9049653</t>
+          <t xml:space="preserve">737562, 5238011</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H140">
-        <v>664</v>
+        <v>1394</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311770634</t>
+          <t xml:space="preserve">311772649</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-07-02</t>
+          <t xml:space="preserve">2034-07-10</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -8446,15 +8446,15 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H141">
-        <v>1394</v>
+        <v>1287</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311772649</t>
+          <t xml:space="preserve">311772650</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -8491,35 +8491,35 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slogsherredsvej 41</t>
+          <t xml:space="preserve">Møllemærsk 24</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t xml:space="preserve">6372</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">737562, 5238011</t>
+          <t xml:space="preserve">309127, 309128, 309129</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H142">
-        <v>1287</v>
+        <v>5924</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311772650</t>
+          <t xml:space="preserve">311783172</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-07-10</t>
+          <t xml:space="preserve">2034-09-06</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirketoften 10</t>
+          <t xml:space="preserve">Kirkeplads 3A</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -8621,7 +8621,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">5252364</t>
+          <t xml:space="preserve">5774705</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -8630,11 +8630,11 @@
         </is>
       </c>
       <c r="H144">
-        <v>325</v>
+        <v>408</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813574</t>
+          <t xml:space="preserve">311813570</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirketoften 20</t>
+          <t xml:space="preserve">Kirketoften 10</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H145">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirketoften 30</t>
+          <t xml:space="preserve">Kirketoften 20</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H146">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirketoften 40</t>
+          <t xml:space="preserve">Kirketoften 30</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -8806,15 +8806,15 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H147">
-        <v>360</v>
+        <v>325</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813682</t>
+          <t xml:space="preserve">311813574</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirketoften 50</t>
+          <t xml:space="preserve">Kirketoften 40</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H148">
@@ -8911,7 +8911,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirketoften 60</t>
+          <t xml:space="preserve">Kirketoften 50</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -8926,15 +8926,15 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H149">
-        <v>1635</v>
+        <v>360</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813683</t>
+          <t xml:space="preserve">311813682</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkeplads 3A</t>
+          <t xml:space="preserve">Kirketoften 60</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -8981,20 +8981,20 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">5774705</t>
+          <t xml:space="preserve">5252364</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H150">
-        <v>408</v>
+        <v>1635</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813570</t>
+          <t xml:space="preserve">311813683</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langrode 9A</t>
+          <t xml:space="preserve">Langrode 7A</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9226,7 +9226,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H154">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langrode 7A</t>
+          <t xml:space="preserve">Langrode 9A</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9286,7 +9286,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="H155">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Harkærvej 19</t>
+          <t xml:space="preserve">Harkærvej 13</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9341,20 +9341,20 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">737430, 1808354</t>
+          <t xml:space="preserve">737434, 1808354</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H156">
-        <v>442</v>
+        <v>1934</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814771</t>
+          <t xml:space="preserve">311814773</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -9406,11 +9406,11 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H157">
-        <v>1934</v>
+        <v>1343</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -9466,11 +9466,11 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H158">
-        <v>1343</v>
+        <v>3168</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -9526,15 +9526,15 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H159">
-        <v>3168</v>
+        <v>895</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814773</t>
+          <t xml:space="preserve">311814770</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -9571,7 +9571,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Harkærvej 13</t>
+          <t xml:space="preserve">Harkærvej 19</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -9581,20 +9581,20 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">737434, 1808354</t>
+          <t xml:space="preserve">737430, 1808354</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H160">
-        <v>895</v>
+        <v>442</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814770</t>
+          <t xml:space="preserve">311814771</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stubbæk Skolegade 1</t>
+          <t xml:space="preserve">Nyløkke 17</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -9821,20 +9821,20 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">5265175</t>
+          <t xml:space="preserve">5780157</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H164">
-        <v>373</v>
+        <v>280</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821030</t>
+          <t xml:space="preserve">311821028</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -9871,7 +9871,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søstvej 11</t>
+          <t xml:space="preserve">Stubbæk Skolegade 1</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -9881,20 +9881,20 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">5779435</t>
+          <t xml:space="preserve">5265175</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H165">
-        <v>624</v>
+        <v>373</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821027</t>
+          <t xml:space="preserve">311821030</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyløkke 17</t>
+          <t xml:space="preserve">Søstvej 11</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">5780157</t>
+          <t xml:space="preserve">5779435</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -9950,11 +9950,11 @@
         </is>
       </c>
       <c r="H166">
-        <v>280</v>
+        <v>624</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821028</t>
+          <t xml:space="preserve">311821027</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -9991,7 +9991,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stubbæk Skolegade 8</t>
+          <t xml:space="preserve">Nygade 21</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -10001,20 +10001,20 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">5265545</t>
+          <t xml:space="preserve">5774474</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H167">
-        <v>666</v>
+        <v>1330</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831237</t>
+          <t xml:space="preserve">311831290</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -10051,7 +10051,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stubbæk Bygade 1</t>
+          <t xml:space="preserve">Nygade 23A</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10061,7 +10061,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">5265560</t>
+          <t xml:space="preserve">5774474</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -10070,11 +10070,11 @@
         </is>
       </c>
       <c r="H168">
-        <v>790</v>
+        <v>2030</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831239</t>
+          <t xml:space="preserve">311831286</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 23A</t>
+          <t xml:space="preserve">Nygade 23C</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -10126,15 +10126,15 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H169">
-        <v>2030</v>
+        <v>1623</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831286</t>
+          <t xml:space="preserve">311831291</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -10171,7 +10171,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 21</t>
+          <t xml:space="preserve">Nygade 23D</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -10186,15 +10186,15 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H170">
-        <v>1330</v>
+        <v>1076</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831290</t>
+          <t xml:space="preserve">311831292</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 23C</t>
+          <t xml:space="preserve">Stubbæk Bygade 1</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10241,20 +10241,20 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">5774474</t>
+          <t xml:space="preserve">5265560</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H171">
-        <v>1623</v>
+        <v>790</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831291</t>
+          <t xml:space="preserve">311831239</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 23D</t>
+          <t xml:space="preserve">Stubbæk Skolegade 8</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10301,20 +10301,20 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">5774474</t>
+          <t xml:space="preserve">5265545</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H172">
-        <v>1076</v>
+        <v>666</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831292</t>
+          <t xml:space="preserve">311831237</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tøndervej 92</t>
+          <t xml:space="preserve">Tøndervej 90</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -10546,15 +10546,15 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H176">
-        <v>762</v>
+        <v>2476</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831294</t>
+          <t xml:space="preserve">311831283</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tøndervej 90</t>
+          <t xml:space="preserve">Tøndervej 92</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -10606,15 +10606,15 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H177">
-        <v>2476</v>
+        <v>762</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831283</t>
+          <t xml:space="preserve">311831294</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 33</t>
+          <t xml:space="preserve">Bjerggade 4E</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -11081,20 +11081,20 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">100006578</t>
+          <t xml:space="preserve">9058289</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H185">
-        <v>1429</v>
+        <v>610</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868875</t>
+          <t xml:space="preserve">311868873</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -11131,7 +11131,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 33</t>
+          <t xml:space="preserve">Bjerggade 4F</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -11141,20 +11141,20 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">100006578</t>
+          <t xml:space="preserve">9058289</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H186">
-        <v>860</v>
+        <v>1113</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868877</t>
+          <t xml:space="preserve">311868873</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -11191,7 +11191,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjerggade 8</t>
+          <t xml:space="preserve">Bjerggade 4G</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -11201,20 +11201,20 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">10202622</t>
+          <t xml:space="preserve">9058289</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H187">
-        <v>427</v>
+        <v>604</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868888</t>
+          <t xml:space="preserve">311868873</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -11251,30 +11251,30 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørremarken 44C</t>
+          <t xml:space="preserve">Bjerggade 8</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t xml:space="preserve">6360</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">5242501</t>
+          <t xml:space="preserve">10202622</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H188">
-        <v>1921</v>
+        <v>427</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868868</t>
+          <t xml:space="preserve">311868888</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -11311,17 +11311,17 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørremarken 44A</t>
+          <t xml:space="preserve">Lille Kolstrup 10</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t xml:space="preserve">6360</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">5243868</t>
+          <t xml:space="preserve">5779275</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -11330,11 +11330,11 @@
         </is>
       </c>
       <c r="H189">
-        <v>1263</v>
+        <v>2117</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868866</t>
+          <t xml:space="preserve">311868870</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -11371,17 +11371,17 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 8</t>
+          <t xml:space="preserve">Nørremarken 44A</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6360</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">5245639</t>
+          <t xml:space="preserve">5243868</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -11390,11 +11390,11 @@
         </is>
       </c>
       <c r="H190">
-        <v>805</v>
+        <v>1263</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868878</t>
+          <t xml:space="preserve">311868866</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -11431,30 +11431,30 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 8</t>
+          <t xml:space="preserve">Nørremarken 44C</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6360</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">5245639</t>
+          <t xml:space="preserve">5242501</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H191">
-        <v>650</v>
+        <v>1921</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868878</t>
+          <t xml:space="preserve">311868868</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -11491,7 +11491,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 8</t>
+          <t xml:space="preserve">Skolegade 10</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -11506,15 +11506,15 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H192">
-        <v>454</v>
+        <v>285</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868878</t>
+          <t xml:space="preserve">311868879</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 10</t>
+          <t xml:space="preserve">Skolegade 8</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -11566,15 +11566,15 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H193">
-        <v>285</v>
+        <v>805</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868879</t>
+          <t xml:space="preserve">311868878</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -11611,30 +11611,30 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lille Kolstrup 10</t>
+          <t xml:space="preserve">Skolegade 8</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">5779275</t>
+          <t xml:space="preserve">5245639</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H194">
-        <v>2117</v>
+        <v>650</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868870</t>
+          <t xml:space="preserve">311868878</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -11671,30 +11671,30 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjerggade 4E</t>
+          <t xml:space="preserve">Skolegade 8</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">9058289</t>
+          <t xml:space="preserve">5245639</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H195">
-        <v>610</v>
+        <v>454</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868873</t>
+          <t xml:space="preserve">311868878</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjerggade 4F</t>
+          <t xml:space="preserve">Skolevænget 33</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -11741,20 +11741,20 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">9058289</t>
+          <t xml:space="preserve">100006578</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H196">
-        <v>1113</v>
+        <v>1429</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868873</t>
+          <t xml:space="preserve">311868875</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -11791,7 +11791,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjerggade 4G</t>
+          <t xml:space="preserve">Skolevænget 33</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -11801,20 +11801,20 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">9058289</t>
+          <t xml:space="preserve">100006578</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H197">
-        <v>604</v>
+        <v>860</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868873</t>
+          <t xml:space="preserve">311868877</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -11911,30 +11911,30 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åbjerg 8B</t>
+          <t xml:space="preserve">Bjerggade 4C</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t xml:space="preserve">6340</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">5263733</t>
+          <t xml:space="preserve">9058289</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H199">
-        <v>853</v>
+        <v>891</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875352</t>
+          <t xml:space="preserve">311875341</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -11971,30 +11971,30 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åbjerg 8B</t>
+          <t xml:space="preserve">Bladknæk 51</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t xml:space="preserve">6340</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">5263733</t>
+          <t xml:space="preserve">8114886</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H200">
-        <v>1115</v>
+        <v>944</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875352</t>
+          <t xml:space="preserve">311875347</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -12031,30 +12031,30 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åbjerg 8B</t>
+          <t xml:space="preserve">Byvænget 4</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t xml:space="preserve">6340</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">5263733</t>
+          <t xml:space="preserve">8052209</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H201">
-        <v>381</v>
+        <v>352</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875352</t>
+          <t xml:space="preserve">311875338</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -12091,30 +12091,30 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åbjerg 8B</t>
+          <t xml:space="preserve">Fjordløkke 1</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t xml:space="preserve">6340</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">5263733</t>
+          <t xml:space="preserve">5777609</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H202">
-        <v>445</v>
+        <v>540</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875352</t>
+          <t xml:space="preserve">311875336</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -12151,30 +12151,30 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åbjerg 8B</t>
+          <t xml:space="preserve">Langebro 22</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t xml:space="preserve">6340</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t xml:space="preserve">5263733</t>
+          <t xml:space="preserve">5776990</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H203">
-        <v>925</v>
+        <v>592</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875352</t>
+          <t xml:space="preserve">311875353</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -12211,30 +12211,30 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åbjerg 8B</t>
+          <t xml:space="preserve">Lergård 2</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t xml:space="preserve">6340</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t xml:space="preserve">5263733</t>
+          <t xml:space="preserve">7681750</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H204">
-        <v>405</v>
+        <v>589</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875352</t>
+          <t xml:space="preserve">311875339</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -12271,30 +12271,30 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åbjerg 8B</t>
+          <t xml:space="preserve">Nygade 46</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t xml:space="preserve">6340</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t xml:space="preserve">5263733</t>
+          <t xml:space="preserve">7791737</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H205">
-        <v>2453</v>
+        <v>556</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875352</t>
+          <t xml:space="preserve">311875342</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -12331,7 +12331,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestvejen 25</t>
+          <t xml:space="preserve">Posekærvej 20</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -12341,20 +12341,20 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">5776345</t>
+          <t xml:space="preserve">5776859</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H206">
-        <v>1081</v>
+        <v>1615</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875335</t>
+          <t xml:space="preserve">311875334</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -12391,7 +12391,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Posekærvej 20</t>
+          <t xml:space="preserve">Præsteskoven 40</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -12401,20 +12401,20 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">5776859</t>
+          <t xml:space="preserve">9392994</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H207">
-        <v>1615</v>
+        <v>690</v>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875334</t>
+          <t xml:space="preserve">311875343</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -12451,7 +12451,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langebro 22</t>
+          <t xml:space="preserve">Sejsbjerg 16</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -12461,7 +12461,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t xml:space="preserve">5776990</t>
+          <t xml:space="preserve">8353545</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -12470,11 +12470,11 @@
         </is>
       </c>
       <c r="H208">
-        <v>592</v>
+        <v>741</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875353</t>
+          <t xml:space="preserve">311875345</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -12511,7 +12511,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fjordløkke 1</t>
+          <t xml:space="preserve">Vestvejen 25</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -12521,20 +12521,20 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777609</t>
+          <t xml:space="preserve">5776345</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H209">
-        <v>540</v>
+        <v>1081</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875336</t>
+          <t xml:space="preserve">311875335</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -12571,17 +12571,17 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lergård 2</t>
+          <t xml:space="preserve">Åbjerg 8B</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6340</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t xml:space="preserve">7681750</t>
+          <t xml:space="preserve">5263733</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -12590,11 +12590,11 @@
         </is>
       </c>
       <c r="H210">
-        <v>589</v>
+        <v>853</v>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875339</t>
+          <t xml:space="preserve">311875352</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -12631,30 +12631,30 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 46</t>
+          <t xml:space="preserve">Åbjerg 8B</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6340</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t xml:space="preserve">7791737</t>
+          <t xml:space="preserve">5263733</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H211">
-        <v>556</v>
+        <v>1115</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875342</t>
+          <t xml:space="preserve">311875352</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -12691,30 +12691,30 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvænget 4</t>
+          <t xml:space="preserve">Åbjerg 8B</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6340</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">8052209</t>
+          <t xml:space="preserve">5263733</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H212">
-        <v>352</v>
+        <v>381</v>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875338</t>
+          <t xml:space="preserve">311875352</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -12751,30 +12751,30 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bladknæk 51</t>
+          <t xml:space="preserve">Åbjerg 8B</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6340</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t xml:space="preserve">8114886</t>
+          <t xml:space="preserve">5263733</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H213">
-        <v>944</v>
+        <v>445</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875347</t>
+          <t xml:space="preserve">311875352</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -12811,30 +12811,30 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sejsbjerg 16</t>
+          <t xml:space="preserve">Åbjerg 8B</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6340</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t xml:space="preserve">8353545</t>
+          <t xml:space="preserve">5263733</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H214">
-        <v>741</v>
+        <v>925</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875345</t>
+          <t xml:space="preserve">311875352</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -12871,30 +12871,30 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjerggade 4C</t>
+          <t xml:space="preserve">Åbjerg 8B</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6340</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t xml:space="preserve">9058289</t>
+          <t xml:space="preserve">5263733</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H215">
-        <v>891</v>
+        <v>405</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875341</t>
+          <t xml:space="preserve">311875352</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -12931,30 +12931,30 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præsteskoven 40</t>
+          <t xml:space="preserve">Åbjerg 8B</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6340</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t xml:space="preserve">9392994</t>
+          <t xml:space="preserve">5263733</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H216">
-        <v>690</v>
+        <v>2453</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875343</t>
+          <t xml:space="preserve">311875352</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -13171,7 +13171,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stubbæk Skolegade 3</t>
+          <t xml:space="preserve">Dronning Margrethes Vej 13</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -13181,7 +13181,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t xml:space="preserve">5265175</t>
+          <t xml:space="preserve">5776972</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -13190,11 +13190,11 @@
         </is>
       </c>
       <c r="H220">
-        <v>1592</v>
+        <v>6714</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888543</t>
+          <t xml:space="preserve">311888544</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -13246,11 +13246,11 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H221">
-        <v>723</v>
+        <v>1592</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
@@ -13306,11 +13306,11 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H222">
-        <v>2411</v>
+        <v>723</v>
       </c>
       <c r="I222" t="inlineStr">
         <is>
@@ -13351,7 +13351,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronning Margrethes Vej 13</t>
+          <t xml:space="preserve">Stubbæk Skolegade 3</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -13361,20 +13361,20 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t xml:space="preserve">5776972</t>
+          <t xml:space="preserve">5265175</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H223">
-        <v>6714</v>
+        <v>2411</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888544</t>
+          <t xml:space="preserve">311888543</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">

--- a/public/exports/29189854.xlsx
+++ b/public/exports/29189854.xlsx
@@ -2454,7 +2454,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661158</t>
+          <t xml:space="preserve">311661159</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670164</t>
+          <t xml:space="preserve">311670161</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670164</t>
+          <t xml:space="preserve">311670161</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670164</t>
+          <t xml:space="preserve">311670161</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670164</t>
+          <t xml:space="preserve">311670161</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813816</t>
+          <t xml:space="preserve">311813855</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813818</t>
+          <t xml:space="preserve">311813855</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -9294,7 +9294,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813818</t>
+          <t xml:space="preserve">311813855</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">

--- a/public/exports/29189854.xlsx
+++ b/public/exports/29189854.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L223"/>
+  <dimension ref="A1:M223"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -664,10 +714,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -724,10 +779,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -779,15 +839,20 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t xml:space="preserve">2018-10-29</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -839,15 +904,20 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Just A/S</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-06-03</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -899,15 +969,20 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t xml:space="preserve">ingeniørgruppen syd</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-02-24</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -959,15 +1034,20 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-04-16</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1019,15 +1099,20 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tetcon A/S</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-11-06</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1079,15 +1164,20 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t xml:space="preserve">ingeniørgruppen syd</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-03-02</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1139,15 +1229,20 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vh-consult</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-02-06</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1199,15 +1294,20 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-06-24</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1259,15 +1359,20 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t xml:space="preserve">Elmlund Erhverv v/Carsten E Rasmussen</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-07-02</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1319,15 +1424,20 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vh-consult</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-05-06</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1379,15 +1489,20 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vh-consult</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-25</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1439,15 +1554,20 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-25</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1499,15 +1619,20 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-25</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1559,15 +1684,20 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-25</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1619,15 +1749,20 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-02-13</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1679,15 +1814,20 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-02-13</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1739,15 +1879,20 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-02-15</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1799,15 +1944,20 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-20</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1859,15 +2009,20 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-22</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1919,15 +2074,20 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-20</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1979,15 +2139,20 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-20</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2039,15 +2204,20 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-20</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2099,15 +2269,20 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-13</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2159,15 +2334,20 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vh-consult</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-16</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2219,15 +2399,20 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vh-consult</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-16</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2279,15 +2464,20 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-18</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2339,15 +2529,20 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-20</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2399,15 +2594,20 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-20</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2459,15 +2659,20 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-20</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2519,15 +2724,20 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-20</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2579,15 +2789,20 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-22</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2639,15 +2854,20 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-22</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2699,15 +2919,20 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-22</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2759,15 +2984,20 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-22</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2819,15 +3049,20 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-22</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2879,15 +3114,20 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-22</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2939,15 +3179,20 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-23</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2999,15 +3244,20 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-23</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3059,15 +3309,20 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-21</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3119,15 +3374,20 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-21</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3179,15 +3439,20 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-21</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3239,15 +3504,20 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-21</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3299,15 +3569,20 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-22</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3359,15 +3634,20 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-22</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3419,15 +3699,20 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3479,15 +3764,20 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3539,15 +3829,20 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3599,15 +3894,20 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3659,15 +3959,20 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3714,20 +4019,25 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670165</t>
+          <t xml:space="preserve">311670161</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3779,15 +4089,20 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3839,15 +4154,20 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3899,15 +4219,20 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3959,15 +4284,20 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4019,15 +4349,20 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4079,15 +4414,20 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4139,15 +4479,20 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4199,15 +4544,20 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4259,15 +4609,20 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-30</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4319,15 +4674,20 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-30</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4379,15 +4739,20 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-30</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4434,20 +4799,25 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311673018</t>
+          <t xml:space="preserve">311673019</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-12</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4494,20 +4864,25 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311673018</t>
+          <t xml:space="preserve">311673019</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-12</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4554,20 +4929,25 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311673018</t>
+          <t xml:space="preserve">311673019</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-12</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4619,15 +4999,20 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-08</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4679,15 +5064,20 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-08</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4739,15 +5129,20 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-08</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4799,15 +5194,20 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-08</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4859,15 +5259,20 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-11</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4919,15 +5324,20 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-11</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4979,15 +5389,20 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-30</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5039,15 +5454,20 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-30</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5099,15 +5519,20 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-30</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5159,15 +5584,20 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-30</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5219,15 +5649,20 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-07-27</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5279,15 +5714,20 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-11</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5339,15 +5779,20 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-25</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5399,15 +5844,20 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-03</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5459,15 +5909,20 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-03</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5519,15 +5974,20 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-03</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5579,15 +6039,20 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-03</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5639,15 +6104,20 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-03</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5699,15 +6169,20 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-03</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5759,15 +6234,20 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-03</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5819,15 +6299,20 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-03</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5879,15 +6364,20 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
+          <t xml:space="preserve">Total-Tjek</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-03</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5939,15 +6429,20 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-03</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5999,15 +6494,20 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-03</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6059,15 +6559,20 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-03</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6119,15 +6624,20 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-03</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6179,15 +6689,20 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-03</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6239,15 +6754,20 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-06</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6299,15 +6819,20 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-06</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6359,15 +6884,20 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-06</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6419,15 +6949,20 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-06</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6479,15 +7014,20 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-06</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6539,15 +7079,20 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-06</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6594,20 +7139,25 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311764474</t>
+          <t xml:space="preserve">311764473</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-06</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6654,20 +7204,25 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311764474</t>
+          <t xml:space="preserve">311764473</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-06</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6719,15 +7274,20 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-07</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6779,15 +7339,20 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-07</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6839,15 +7404,20 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-14</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6899,15 +7469,20 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-14</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6959,15 +7534,20 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-14</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7019,15 +7599,20 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-14</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7079,15 +7664,20 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-14</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7139,15 +7729,20 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-14</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7199,15 +7794,20 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-14</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7259,15 +7859,20 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-14</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7319,15 +7924,20 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-14</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7379,15 +7989,20 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-14</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7439,15 +8054,20 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-14</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7499,15 +8119,20 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-14</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7559,15 +8184,20 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-14</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7619,15 +8249,20 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-14</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7674,20 +8309,25 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311767653</t>
+          <t xml:space="preserve">311767649</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-19</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7734,20 +8374,25 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311767653</t>
+          <t xml:space="preserve">311767649</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-19</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7799,15 +8444,20 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-19</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7859,15 +8509,20 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-19</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7919,15 +8574,20 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-19</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7979,15 +8639,20 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-20</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8039,15 +8704,20 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-20</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8099,15 +8769,20 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-20</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8159,15 +8834,20 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-25</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8219,15 +8899,20 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-07-02</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8279,15 +8964,20 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-07-02</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8339,15 +9029,20 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-07-02</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8399,15 +9094,20 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-07-10</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8459,15 +9159,20 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-07-10</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8519,15 +9224,20 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-09-06</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8579,15 +9289,20 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-10-17</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8639,15 +9354,20 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-24</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8699,15 +9419,20 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-24</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8759,15 +9484,20 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-24</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8819,15 +9549,20 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-24</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8879,15 +9614,20 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-24</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8939,15 +9679,20 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-24</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8999,15 +9744,20 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-24</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9059,15 +9809,20 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-24</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9119,15 +9874,20 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-25</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9179,15 +9939,20 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-25</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9239,15 +10004,20 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-25</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9299,15 +10069,20 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-25</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9354,20 +10129,25 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814773</t>
+          <t xml:space="preserve">311814771</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-28</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9414,20 +10194,25 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814773</t>
+          <t xml:space="preserve">311814771</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-28</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9474,20 +10259,25 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814773</t>
+          <t xml:space="preserve">311814771</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-28</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9534,20 +10324,25 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814770</t>
+          <t xml:space="preserve">311814771</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-28</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9599,15 +10394,20 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-28</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9659,15 +10459,20 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-12</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9719,15 +10524,20 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-28</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9779,15 +10589,20 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-28</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9839,15 +10654,20 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-28</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9899,15 +10719,20 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-28</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9959,15 +10784,20 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-28</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10019,15 +10849,20 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-13</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10079,15 +10914,20 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-13</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10139,15 +10979,20 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-13</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10199,15 +11044,20 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-13</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10259,15 +11109,20 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-13</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10319,15 +11174,20 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-13</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10379,15 +11239,20 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-13</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10439,15 +11304,20 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-13</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10499,15 +11369,20 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-13</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10559,15 +11434,20 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-13</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10619,15 +11499,20 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-13</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10679,15 +11564,20 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-14</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10739,15 +11629,20 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-14</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10799,15 +11694,20 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-14</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10859,15 +11759,20 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-14</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10919,15 +11824,20 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-15</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10979,15 +11889,20 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-15</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11039,15 +11954,20 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-15</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11099,15 +12019,20 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-18</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11159,15 +12084,20 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-18</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11219,15 +12149,20 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-18</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11279,15 +12214,20 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-18</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11339,15 +12279,20 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-18</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11399,15 +12344,20 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-18</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11459,15 +12409,20 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-18</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11519,15 +12474,20 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-18</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11579,15 +12539,20 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-18</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11639,15 +12604,20 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-18</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11699,15 +12669,20 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-18</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11759,15 +12734,20 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-18</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11819,15 +12799,20 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-18</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11879,15 +12864,20 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-04</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11939,15 +12929,20 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-06</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11999,15 +12994,20 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-06</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12059,15 +13059,20 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-06</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12119,15 +13124,20 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-06</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12179,15 +13189,20 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-06</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12239,15 +13254,20 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-06</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12299,15 +13319,20 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-06</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12359,15 +13384,20 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-06</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12419,15 +13449,20 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-06</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12479,15 +13514,20 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-06</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12539,15 +13579,20 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-06</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12599,15 +13644,20 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-06</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12659,15 +13709,20 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-06</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12719,15 +13774,20 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-06</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12779,15 +13839,20 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-06</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12839,15 +13904,20 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-06</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12899,15 +13969,20 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-06</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12959,15 +14034,20 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-06</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13019,15 +14099,20 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-05</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13079,15 +14164,20 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-05</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13139,15 +14229,20 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ingeniørgruppen Haderslev ApS</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-11</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13199,15 +14294,20 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-19</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13259,15 +14359,20 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-19</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13319,15 +14424,20 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-19</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13379,21 +14489,26 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-19</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L223" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L223"/>
+  <autoFilter ref="A1:M223"/>
 </worksheet>
 </file>
--- a/public/exports/29189854.xlsx
+++ b/public/exports/29189854.xlsx
@@ -2654,7 +2654,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661159</t>
+          <t xml:space="preserve">311661158</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311673019</t>
+          <t xml:space="preserve">311673018</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311673019</t>
+          <t xml:space="preserve">311673018</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311673019</t>
+          <t xml:space="preserve">311673018</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9934,12 +9934,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813855</t>
+          <t xml:space="preserve">311813816</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813855</t>
+          <t xml:space="preserve">311813818</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -10064,12 +10064,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813855</t>
+          <t xml:space="preserve">311813818</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -10324,7 +10324,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814771</t>
+          <t xml:space="preserve">311814770</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
